--- a/2026.xlsx
+++ b/2026.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10919"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{F97ADF32-5DA8-504E-A49E-1229F0068FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAE3492D-1C2B-5046-A287-0E3A477DA032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2286" uniqueCount="1904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2286" uniqueCount="749">
   <si>
     <t>SELECTION 1</t>
   </si>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="M103" s="1"/>
       <c r="N103" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O103" s="1" t="s">
         <v>24</v>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -545,12 +545,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -545,12 +545,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\portn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCA48CC9-70F0-4837-A8C6-E869F554E594}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3437" uniqueCount="1276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3435" uniqueCount="1275">
   <si>
     <t>SELECTION 1</t>
   </si>
@@ -3252,9 +3252,6 @@
   </si>
   <si>
     <t>106</t>
-  </si>
-  <si>
-    <t>01.01.1900</t>
   </si>
   <si>
     <t>77955</t>
@@ -3896,8 +3893,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -4206,6 +4204,7 @@
     <col min="4" max="4" width="34.83984375" customWidth="1"/>
     <col min="5" max="5" width="25.83984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="34.41796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.62890625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.20703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.83984375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.41796875" bestFit="1" customWidth="1"/>
@@ -10969,8 +10968,8 @@
       <c r="F107" t="s">
         <v>590</v>
       </c>
-      <c r="G107" t="s">
-        <v>1073</v>
+      <c r="G107" s="1">
+        <v>45934</v>
       </c>
       <c r="H107" t="s">
         <v>29</v>
@@ -11006,7 +11005,7 @@
         <v>126</v>
       </c>
       <c r="U107" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="V107" t="s">
         <v>594</v>
@@ -11017,10 +11016,10 @@
     </row>
     <row r="108" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C108" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D108" t="s">
         <v>1075</v>
-      </c>
-      <c r="D108" t="s">
-        <v>1076</v>
       </c>
       <c r="E108" t="s">
         <v>194</v>
@@ -11029,7 +11028,7 @@
         <v>595</v>
       </c>
       <c r="G108" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H108" t="s">
         <v>25</v>
@@ -11068,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="U108" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="V108" t="s">
         <v>198</v>
@@ -11082,10 +11081,10 @@
     </row>
     <row r="109" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C109" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D109" t="s">
         <v>1079</v>
-      </c>
-      <c r="D109" t="s">
-        <v>1080</v>
       </c>
       <c r="E109" t="s">
         <v>596</v>
@@ -11093,8 +11092,8 @@
       <c r="F109" t="s">
         <v>597</v>
       </c>
-      <c r="G109" t="s">
-        <v>1081</v>
+      <c r="G109" s="1">
+        <v>45748</v>
       </c>
       <c r="H109" t="s">
         <v>25</v>
@@ -11133,7 +11132,7 @@
         <v>27</v>
       </c>
       <c r="U109" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="V109" t="s">
         <v>601</v>
@@ -11147,10 +11146,10 @@
     </row>
     <row r="110" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C110" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D110" t="s">
         <v>1083</v>
-      </c>
-      <c r="D110" t="s">
-        <v>1084</v>
       </c>
       <c r="E110" t="s">
         <v>602</v>
@@ -11198,7 +11197,7 @@
         <v>27</v>
       </c>
       <c r="U110" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="V110" t="s">
         <v>198</v>
@@ -11212,10 +11211,10 @@
     </row>
     <row r="111" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C111" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D111" t="s">
         <v>1085</v>
-      </c>
-      <c r="D111" t="s">
-        <v>1086</v>
       </c>
       <c r="E111" t="s">
         <v>604</v>
@@ -11263,7 +11262,7 @@
         <v>27</v>
       </c>
       <c r="U111" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="V111" t="s">
         <v>198</v>
@@ -11277,10 +11276,10 @@
     </row>
     <row r="112" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C112" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D112" t="s">
         <v>1087</v>
-      </c>
-      <c r="D112" t="s">
-        <v>1088</v>
       </c>
       <c r="E112" t="s">
         <v>606</v>
@@ -11289,7 +11288,7 @@
         <v>607</v>
       </c>
       <c r="G112" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H112" t="s">
         <v>29</v>
@@ -11328,7 +11327,7 @@
         <v>27</v>
       </c>
       <c r="U112" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="V112" t="s">
         <v>601</v>
@@ -11342,10 +11341,10 @@
     </row>
     <row r="113" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C113" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D113" t="s">
         <v>1090</v>
-      </c>
-      <c r="D113" t="s">
-        <v>1091</v>
       </c>
       <c r="E113" t="s">
         <v>608</v>
@@ -11354,7 +11353,7 @@
         <v>609</v>
       </c>
       <c r="G113" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H113" t="s">
         <v>29</v>
@@ -11393,7 +11392,7 @@
         <v>27</v>
       </c>
       <c r="U113" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="V113" t="s">
         <v>601</v>
@@ -11407,10 +11406,10 @@
     </row>
     <row r="114" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C114" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D114" t="s">
         <v>1092</v>
-      </c>
-      <c r="D114" t="s">
-        <v>1093</v>
       </c>
       <c r="E114" t="s">
         <v>610</v>
@@ -11419,7 +11418,7 @@
         <v>611</v>
       </c>
       <c r="G114" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H114" t="s">
         <v>25</v>
@@ -11458,7 +11457,7 @@
         <v>27</v>
       </c>
       <c r="U114" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="V114" t="s">
         <v>601</v>
@@ -11472,10 +11471,10 @@
     </row>
     <row r="115" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C115" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D115" t="s">
         <v>1094</v>
-      </c>
-      <c r="D115" t="s">
-        <v>1095</v>
       </c>
       <c r="E115" t="s">
         <v>612</v>
@@ -11484,7 +11483,7 @@
         <v>613</v>
       </c>
       <c r="G115" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H115" t="s">
         <v>29</v>
@@ -11520,7 +11519,7 @@
         <v>27</v>
       </c>
       <c r="U115" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="V115" t="s">
         <v>617</v>
@@ -11531,10 +11530,10 @@
     </row>
     <row r="116" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C116" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D116" t="s">
         <v>1098</v>
-      </c>
-      <c r="D116" t="s">
-        <v>1099</v>
       </c>
       <c r="E116" t="s">
         <v>200</v>
@@ -11543,7 +11542,7 @@
         <v>618</v>
       </c>
       <c r="G116" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H116" t="s">
         <v>29</v>
@@ -11585,7 +11584,7 @@
         <v>27</v>
       </c>
       <c r="U116" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="V116" t="s">
         <v>204</v>
@@ -11599,10 +11598,10 @@
     </row>
     <row r="117" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C117" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D117" t="s">
         <v>1102</v>
-      </c>
-      <c r="D117" t="s">
-        <v>1103</v>
       </c>
       <c r="E117" t="s">
         <v>205</v>
@@ -11611,7 +11610,7 @@
         <v>619</v>
       </c>
       <c r="G117" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H117" t="s">
         <v>29</v>
@@ -11650,7 +11649,7 @@
         <v>27</v>
       </c>
       <c r="U117" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="V117" t="s">
         <v>204</v>
@@ -11664,10 +11663,10 @@
     </row>
     <row r="118" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C118" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D118" t="s">
         <v>1105</v>
-      </c>
-      <c r="D118" t="s">
-        <v>1106</v>
       </c>
       <c r="E118" t="s">
         <v>620</v>
@@ -11715,7 +11714,7 @@
         <v>27</v>
       </c>
       <c r="U118" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="V118" t="s">
         <v>204</v>
@@ -11729,10 +11728,10 @@
     </row>
     <row r="119" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C119" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D119" t="s">
         <v>1107</v>
-      </c>
-      <c r="D119" t="s">
-        <v>1108</v>
       </c>
       <c r="E119" t="s">
         <v>623</v>
@@ -11741,7 +11740,7 @@
         <v>624</v>
       </c>
       <c r="G119" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H119" t="s">
         <v>29</v>
@@ -11780,7 +11779,7 @@
         <v>27</v>
       </c>
       <c r="U119" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="V119" t="s">
         <v>215</v>
@@ -11794,10 +11793,10 @@
     </row>
     <row r="120" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C120" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D120" t="s">
         <v>1111</v>
-      </c>
-      <c r="D120" t="s">
-        <v>1112</v>
       </c>
       <c r="E120" t="s">
         <v>625</v>
@@ -11806,7 +11805,7 @@
         <v>626</v>
       </c>
       <c r="G120" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H120" t="s">
         <v>29</v>
@@ -11842,7 +11841,7 @@
         <v>27</v>
       </c>
       <c r="U120" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="V120" t="s">
         <v>630</v>
@@ -11853,10 +11852,10 @@
     </row>
     <row r="121" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C121" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D121" t="s">
         <v>1115</v>
-      </c>
-      <c r="D121" t="s">
-        <v>1116</v>
       </c>
       <c r="E121" t="s">
         <v>631</v>
@@ -11865,7 +11864,7 @@
         <v>632</v>
       </c>
       <c r="G121" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H121" t="s">
         <v>29</v>
@@ -11901,7 +11900,7 @@
         <v>27</v>
       </c>
       <c r="U121" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="V121" t="s">
         <v>630</v>
@@ -11912,10 +11911,10 @@
     </row>
     <row r="122" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C122" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D122" t="s">
         <v>1118</v>
-      </c>
-      <c r="D122" t="s">
-        <v>1119</v>
       </c>
       <c r="E122" t="s">
         <v>633</v>
@@ -11963,7 +11962,7 @@
         <v>27</v>
       </c>
       <c r="U122" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="V122" t="s">
         <v>215</v>
@@ -11977,10 +11976,10 @@
     </row>
     <row r="123" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C123" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D123" t="s">
         <v>1120</v>
-      </c>
-      <c r="D123" t="s">
-        <v>1121</v>
       </c>
       <c r="E123" t="s">
         <v>635</v>
@@ -11989,7 +11988,7 @@
         <v>636</v>
       </c>
       <c r="G123" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H123" t="s">
         <v>29</v>
@@ -12025,7 +12024,7 @@
         <v>27</v>
       </c>
       <c r="U123" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="V123" t="s">
         <v>630</v>
@@ -12036,7 +12035,7 @@
     </row>
     <row r="124" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C124" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D124" t="s">
         <v>744</v>
@@ -12084,7 +12083,7 @@
         <v>126</v>
       </c>
       <c r="U124" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="V124" t="s">
         <v>594</v>
@@ -12095,10 +12094,10 @@
     </row>
     <row r="125" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C125" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D125" t="s">
         <v>1123</v>
-      </c>
-      <c r="D125" t="s">
-        <v>1124</v>
       </c>
       <c r="E125" t="s">
         <v>640</v>
@@ -12107,7 +12106,7 @@
         <v>641</v>
       </c>
       <c r="G125" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H125" t="s">
         <v>25</v>
@@ -12143,7 +12142,7 @@
         <v>126</v>
       </c>
       <c r="U125" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="V125" t="s">
         <v>646</v>
@@ -12154,10 +12153,10 @@
     </row>
     <row r="126" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C126" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D126" t="s">
         <v>1127</v>
-      </c>
-      <c r="D126" t="s">
-        <v>1128</v>
       </c>
       <c r="E126" t="s">
         <v>647</v>
@@ -12202,7 +12201,7 @@
         <v>126</v>
       </c>
       <c r="U126" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="V126" t="s">
         <v>646</v>
@@ -12213,10 +12212,10 @@
     </row>
     <row r="127" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C127" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D127" t="s">
         <v>1129</v>
-      </c>
-      <c r="D127" t="s">
-        <v>1130</v>
       </c>
       <c r="E127" t="s">
         <v>649</v>
@@ -12225,7 +12224,7 @@
         <v>650</v>
       </c>
       <c r="G127" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H127" t="s">
         <v>25</v>
@@ -12261,7 +12260,7 @@
         <v>27</v>
       </c>
       <c r="U127" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="V127" t="s">
         <v>220</v>
@@ -12275,10 +12274,10 @@
     </row>
     <row r="128" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C128" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D128" t="s">
         <v>1133</v>
-      </c>
-      <c r="D128" t="s">
-        <v>1134</v>
       </c>
       <c r="E128" t="s">
         <v>225</v>
@@ -12323,7 +12322,7 @@
         <v>27</v>
       </c>
       <c r="U128" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="V128" t="s">
         <v>224</v>
@@ -12337,10 +12336,10 @@
     </row>
     <row r="129" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C129" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D129" t="s">
         <v>1136</v>
-      </c>
-      <c r="D129" t="s">
-        <v>1137</v>
       </c>
       <c r="E129" t="s">
         <v>226</v>
@@ -12349,7 +12348,7 @@
         <v>652</v>
       </c>
       <c r="G129" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H129" t="s">
         <v>29</v>
@@ -12385,7 +12384,7 @@
         <v>27</v>
       </c>
       <c r="U129" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="V129" t="s">
         <v>220</v>
@@ -12399,10 +12398,10 @@
     </row>
     <row r="130" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C130" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D130" t="s">
         <v>1139</v>
-      </c>
-      <c r="D130" t="s">
-        <v>1140</v>
       </c>
       <c r="E130" t="s">
         <v>653</v>
@@ -12447,7 +12446,7 @@
         <v>27</v>
       </c>
       <c r="U130" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="V130" t="s">
         <v>659</v>
@@ -12458,10 +12457,10 @@
     </row>
     <row r="131" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C131" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D131" t="s">
         <v>1142</v>
-      </c>
-      <c r="D131" t="s">
-        <v>1143</v>
       </c>
       <c r="E131" t="s">
         <v>660</v>
@@ -12470,7 +12469,7 @@
         <v>661</v>
       </c>
       <c r="G131" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H131" t="s">
         <v>25</v>
@@ -12506,7 +12505,7 @@
         <v>27</v>
       </c>
       <c r="U131" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="V131" t="s">
         <v>659</v>
@@ -12517,10 +12516,10 @@
     </row>
     <row r="132" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C132" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D132" t="s">
         <v>1145</v>
-      </c>
-      <c r="D132" t="s">
-        <v>1146</v>
       </c>
       <c r="E132" t="s">
         <v>232</v>
@@ -12529,7 +12528,7 @@
         <v>662</v>
       </c>
       <c r="G132" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H132" t="s">
         <v>29</v>
@@ -12568,7 +12567,7 @@
         <v>27</v>
       </c>
       <c r="U132" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="V132" t="s">
         <v>231</v>
@@ -12582,10 +12581,10 @@
     </row>
     <row r="133" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C133" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D133" t="s">
         <v>1149</v>
-      </c>
-      <c r="D133" t="s">
-        <v>1150</v>
       </c>
       <c r="E133" t="s">
         <v>663</v>
@@ -12594,7 +12593,7 @@
         <v>664</v>
       </c>
       <c r="G133" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H133" t="s">
         <v>29</v>
@@ -12630,7 +12629,7 @@
         <v>27</v>
       </c>
       <c r="U133" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="V133" t="s">
         <v>220</v>
@@ -12644,10 +12643,10 @@
     </row>
     <row r="134" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C134" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D134" t="s">
         <v>1152</v>
-      </c>
-      <c r="D134" t="s">
-        <v>1153</v>
       </c>
       <c r="E134" t="s">
         <v>665</v>
@@ -12656,7 +12655,7 @@
         <v>666</v>
       </c>
       <c r="G134" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H134" t="s">
         <v>25</v>
@@ -12695,7 +12694,7 @@
         <v>27</v>
       </c>
       <c r="U134" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="V134" t="s">
         <v>220</v>
@@ -12709,10 +12708,10 @@
     </row>
     <row r="135" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C135" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D135" t="s">
         <v>1155</v>
-      </c>
-      <c r="D135" t="s">
-        <v>1156</v>
       </c>
       <c r="E135" t="s">
         <v>667</v>
@@ -12721,7 +12720,7 @@
         <v>668</v>
       </c>
       <c r="G135" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H135" t="s">
         <v>25</v>
@@ -12771,10 +12770,10 @@
     </row>
     <row r="136" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C136" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D136" t="s">
         <v>1157</v>
-      </c>
-      <c r="D136" t="s">
-        <v>1158</v>
       </c>
       <c r="E136" t="s">
         <v>673</v>
@@ -12783,7 +12782,7 @@
         <v>674</v>
       </c>
       <c r="G136" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H136" t="s">
         <v>25</v>
@@ -12836,10 +12835,10 @@
     </row>
     <row r="137" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C137" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D137" t="s">
         <v>1160</v>
-      </c>
-      <c r="D137" t="s">
-        <v>1161</v>
       </c>
       <c r="E137" t="s">
         <v>675</v>
@@ -12884,7 +12883,7 @@
         <v>27</v>
       </c>
       <c r="U137" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="V137" t="s">
         <v>220</v>
@@ -12898,10 +12897,10 @@
     </row>
     <row r="138" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C138" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D138" t="s">
         <v>1162</v>
-      </c>
-      <c r="D138" t="s">
-        <v>1163</v>
       </c>
       <c r="E138" t="s">
         <v>677</v>
@@ -12946,7 +12945,7 @@
         <v>27</v>
       </c>
       <c r="U138" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="V138" t="s">
         <v>220</v>
@@ -12960,10 +12959,10 @@
     </row>
     <row r="139" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C139" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D139" t="s">
         <v>1164</v>
-      </c>
-      <c r="D139" t="s">
-        <v>1165</v>
       </c>
       <c r="E139" t="s">
         <v>679</v>
@@ -12972,7 +12971,7 @@
         <v>680</v>
       </c>
       <c r="G139" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H139" t="s">
         <v>29</v>
@@ -13011,7 +13010,7 @@
         <v>27</v>
       </c>
       <c r="U139" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="V139" t="s">
         <v>237</v>
@@ -13025,10 +13024,10 @@
     </row>
     <row r="140" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C140" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D140" t="s">
         <v>1168</v>
-      </c>
-      <c r="D140" t="s">
-        <v>1169</v>
       </c>
       <c r="E140" t="s">
         <v>681</v>
@@ -13037,7 +13036,7 @@
         <v>682</v>
       </c>
       <c r="G140" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H140" t="s">
         <v>25</v>
@@ -13076,7 +13075,7 @@
         <v>687</v>
       </c>
       <c r="U140" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="V140" t="s">
         <v>688</v>
@@ -13090,10 +13089,10 @@
     </row>
     <row r="141" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C141" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D141" t="s">
         <v>1172</v>
-      </c>
-      <c r="D141" t="s">
-        <v>1173</v>
       </c>
       <c r="E141" t="s">
         <v>689</v>
@@ -13102,7 +13101,7 @@
         <v>690</v>
       </c>
       <c r="G141" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H141" t="s">
         <v>25</v>
@@ -13141,7 +13140,7 @@
         <v>126</v>
       </c>
       <c r="U141" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="V141" t="s">
         <v>250</v>
@@ -13152,7 +13151,7 @@
     </row>
     <row r="142" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C142" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="D142" t="s">
         <v>691</v>
@@ -13203,7 +13202,7 @@
         <v>126</v>
       </c>
       <c r="U142" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="V142" t="s">
         <v>242</v>
@@ -13217,7 +13216,7 @@
     </row>
     <row r="143" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C143" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D143" t="s">
         <v>243</v>
@@ -13229,7 +13228,7 @@
         <v>245</v>
       </c>
       <c r="G143" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H143" t="s">
         <v>25</v>
@@ -13268,7 +13267,7 @@
         <v>126</v>
       </c>
       <c r="U143" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="V143" t="s">
         <v>242</v>
@@ -13282,10 +13281,10 @@
     </row>
     <row r="144" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C144" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D144" t="s">
         <v>1180</v>
-      </c>
-      <c r="D144" t="s">
-        <v>1181</v>
       </c>
       <c r="E144" t="s">
         <v>695</v>
@@ -13294,7 +13293,7 @@
         <v>696</v>
       </c>
       <c r="G144" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H144" t="s">
         <v>25</v>
@@ -13330,7 +13329,7 @@
         <v>126</v>
       </c>
       <c r="U144" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="V144" t="s">
         <v>250</v>
@@ -13341,10 +13340,10 @@
     </row>
     <row r="145" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C145" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D145" t="s">
         <v>1183</v>
-      </c>
-      <c r="D145" t="s">
-        <v>1184</v>
       </c>
       <c r="E145" t="s">
         <v>252</v>
@@ -13353,7 +13352,7 @@
         <v>697</v>
       </c>
       <c r="G145" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H145" t="s">
         <v>25</v>
@@ -13389,7 +13388,7 @@
         <v>27</v>
       </c>
       <c r="U145" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="V145" t="s">
         <v>256</v>
@@ -13400,10 +13399,10 @@
     </row>
     <row r="146" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C146" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D146" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="E146" t="s">
         <v>698</v>
@@ -13412,7 +13411,7 @@
         <v>699</v>
       </c>
       <c r="G146" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H146" t="s">
         <v>29</v>
@@ -13448,7 +13447,7 @@
         <v>126</v>
       </c>
       <c r="U146" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="V146" t="s">
         <v>250</v>
@@ -13459,7 +13458,7 @@
     </row>
     <row r="147" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C147" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="D147" t="s">
         <v>701</v>
@@ -13471,7 +13470,7 @@
         <v>703</v>
       </c>
       <c r="G147" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H147" t="s">
         <v>29</v>
@@ -13510,7 +13509,7 @@
         <v>126</v>
       </c>
       <c r="U147" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="V147" t="s">
         <v>242</v>
@@ -13524,10 +13523,10 @@
     </row>
     <row r="148" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C148" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D148" t="s">
         <v>1190</v>
-      </c>
-      <c r="D148" t="s">
-        <v>1191</v>
       </c>
       <c r="E148" t="s">
         <v>704</v>
@@ -13536,7 +13535,7 @@
         <v>705</v>
       </c>
       <c r="G148" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H148" t="s">
         <v>25</v>
@@ -13572,7 +13571,7 @@
         <v>27</v>
       </c>
       <c r="U148" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="V148" t="s">
         <v>709</v>
@@ -13583,10 +13582,10 @@
     </row>
     <row r="149" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C149" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D149" t="s">
         <v>1194</v>
-      </c>
-      <c r="D149" t="s">
-        <v>1195</v>
       </c>
       <c r="E149" t="s">
         <v>710</v>
@@ -13595,7 +13594,7 @@
         <v>711</v>
       </c>
       <c r="G149" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H149" t="s">
         <v>29</v>
@@ -13631,7 +13630,7 @@
         <v>27</v>
       </c>
       <c r="U149" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="V149" t="s">
         <v>709</v>
@@ -13642,10 +13641,10 @@
     </row>
     <row r="150" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C150" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D150" t="s">
         <v>1197</v>
-      </c>
-      <c r="D150" t="s">
-        <v>1198</v>
       </c>
       <c r="E150" t="s">
         <v>258</v>
@@ -13654,7 +13653,7 @@
         <v>712</v>
       </c>
       <c r="G150" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H150" t="s">
         <v>29</v>
@@ -13693,7 +13692,7 @@
         <v>126</v>
       </c>
       <c r="U150" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="V150" t="s">
         <v>262</v>
@@ -13707,10 +13706,10 @@
     </row>
     <row r="151" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C151" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D151" t="s">
         <v>1201</v>
-      </c>
-      <c r="D151" t="s">
-        <v>1202</v>
       </c>
       <c r="E151" t="s">
         <v>263</v>
@@ -13719,7 +13718,7 @@
         <v>713</v>
       </c>
       <c r="G151" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H151" t="s">
         <v>25</v>
@@ -13758,7 +13757,7 @@
         <v>126</v>
       </c>
       <c r="U151" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="V151" t="s">
         <v>262</v>
@@ -13772,10 +13771,10 @@
     </row>
     <row r="152" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C152" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D152" t="s">
         <v>1204</v>
-      </c>
-      <c r="D152" t="s">
-        <v>1205</v>
       </c>
       <c r="E152" t="s">
         <v>265</v>
@@ -13784,7 +13783,7 @@
         <v>714</v>
       </c>
       <c r="G152" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H152" t="s">
         <v>29</v>
@@ -13823,7 +13822,7 @@
         <v>126</v>
       </c>
       <c r="U152" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="V152" t="s">
         <v>262</v>
@@ -13837,10 +13836,10 @@
     </row>
     <row r="153" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C153" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D153" t="s">
         <v>1206</v>
-      </c>
-      <c r="D153" t="s">
-        <v>1207</v>
       </c>
       <c r="E153" t="s">
         <v>715</v>
@@ -13849,7 +13848,7 @@
         <v>716</v>
       </c>
       <c r="G153" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H153" t="s">
         <v>25</v>
@@ -13888,7 +13887,7 @@
         <v>126</v>
       </c>
       <c r="U153" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="V153" t="s">
         <v>262</v>
@@ -13902,10 +13901,10 @@
     </row>
     <row r="154" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C154" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D154" t="s">
         <v>1209</v>
-      </c>
-      <c r="D154" t="s">
-        <v>1210</v>
       </c>
       <c r="E154" t="s">
         <v>717</v>
@@ -13914,7 +13913,7 @@
         <v>718</v>
       </c>
       <c r="G154" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H154" t="s">
         <v>29</v>
@@ -13953,7 +13952,7 @@
         <v>126</v>
       </c>
       <c r="U154" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="V154" t="s">
         <v>262</v>
@@ -13967,10 +13966,10 @@
     </row>
     <row r="155" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C155" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D155" t="s">
         <v>1212</v>
-      </c>
-      <c r="D155" t="s">
-        <v>1213</v>
       </c>
       <c r="E155" t="s">
         <v>719</v>
@@ -13979,7 +13978,7 @@
         <v>720</v>
       </c>
       <c r="G155" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H155" t="s">
         <v>29</v>
@@ -14018,7 +14017,7 @@
         <v>27</v>
       </c>
       <c r="U155" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="V155" t="s">
         <v>722</v>
@@ -14032,10 +14031,10 @@
     </row>
     <row r="156" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C156" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D156" t="s">
         <v>1216</v>
-      </c>
-      <c r="D156" t="s">
-        <v>1217</v>
       </c>
       <c r="E156" t="s">
         <v>723</v>
@@ -14044,7 +14043,7 @@
         <v>724</v>
       </c>
       <c r="G156" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H156" t="s">
         <v>29</v>
@@ -14083,7 +14082,7 @@
         <v>27</v>
       </c>
       <c r="U156" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="V156" t="s">
         <v>722</v>
@@ -14097,10 +14096,10 @@
     </row>
     <row r="157" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C157" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D157" t="s">
         <v>1219</v>
-      </c>
-      <c r="D157" t="s">
-        <v>1220</v>
       </c>
       <c r="E157" t="s">
         <v>725</v>
@@ -14109,7 +14108,7 @@
         <v>726</v>
       </c>
       <c r="G157" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H157" t="s">
         <v>29</v>
@@ -14148,7 +14147,7 @@
         <v>126</v>
       </c>
       <c r="U157" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="V157" t="s">
         <v>262</v>
@@ -14162,10 +14161,10 @@
     </row>
     <row r="158" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C158" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D158" t="s">
         <v>1222</v>
-      </c>
-      <c r="D158" t="s">
-        <v>1223</v>
       </c>
       <c r="E158" t="s">
         <v>727</v>
@@ -14174,7 +14173,7 @@
         <v>728</v>
       </c>
       <c r="G158" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H158" t="s">
         <v>25</v>
@@ -14213,7 +14212,7 @@
         <v>27</v>
       </c>
       <c r="U158" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="V158" t="s">
         <v>722</v>
@@ -14227,10 +14226,10 @@
     </row>
     <row r="159" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C159" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D159" t="s">
         <v>1225</v>
-      </c>
-      <c r="D159" t="s">
-        <v>1226</v>
       </c>
       <c r="E159" t="s">
         <v>729</v>
@@ -14239,7 +14238,7 @@
         <v>730</v>
       </c>
       <c r="G159" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H159" t="s">
         <v>25</v>
@@ -14278,7 +14277,7 @@
         <v>27</v>
       </c>
       <c r="U159" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="V159" t="s">
         <v>722</v>
@@ -14292,10 +14291,10 @@
     </row>
     <row r="160" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C160" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D160" t="s">
         <v>1228</v>
-      </c>
-      <c r="D160" t="s">
-        <v>1229</v>
       </c>
       <c r="E160" t="s">
         <v>731</v>
@@ -14304,7 +14303,7 @@
         <v>732</v>
       </c>
       <c r="G160" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H160" t="s">
         <v>29</v>
@@ -14343,7 +14342,7 @@
         <v>27</v>
       </c>
       <c r="U160" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="V160" t="s">
         <v>722</v>
@@ -14357,10 +14356,10 @@
     </row>
     <row r="161" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C161" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D161" t="s">
         <v>1231</v>
-      </c>
-      <c r="D161" t="s">
-        <v>1232</v>
       </c>
       <c r="E161" t="s">
         <v>733</v>
@@ -14369,7 +14368,7 @@
         <v>734</v>
       </c>
       <c r="G161" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H161" t="s">
         <v>29</v>
@@ -14408,7 +14407,7 @@
         <v>27</v>
       </c>
       <c r="U161" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="V161" t="s">
         <v>722</v>
@@ -14422,10 +14421,10 @@
     </row>
     <row r="162" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C162" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D162" t="s">
         <v>1234</v>
-      </c>
-      <c r="D162" t="s">
-        <v>1235</v>
       </c>
       <c r="E162" t="s">
         <v>735</v>
@@ -14434,7 +14433,7 @@
         <v>736</v>
       </c>
       <c r="G162" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H162" t="s">
         <v>25</v>
@@ -14473,7 +14472,7 @@
         <v>27</v>
       </c>
       <c r="U162" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="V162" t="s">
         <v>740</v>
@@ -14487,10 +14486,10 @@
     </row>
     <row r="163" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C163" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D163" t="s">
         <v>1238</v>
-      </c>
-      <c r="D163" t="s">
-        <v>1239</v>
       </c>
       <c r="E163" t="s">
         <v>269</v>
@@ -14499,7 +14498,7 @@
         <v>270</v>
       </c>
       <c r="G163" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H163" t="s">
         <v>29</v>
@@ -14535,7 +14534,7 @@
         <v>27</v>
       </c>
       <c r="U163" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="V163" t="s">
         <v>256</v>
@@ -14546,19 +14545,19 @@
     </row>
     <row r="164" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C164" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D164" t="s">
         <v>1241</v>
       </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
         <v>1242</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
         <v>1243</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
         <v>1244</v>
-      </c>
-      <c r="G164" t="s">
-        <v>1245</v>
       </c>
       <c r="H164" t="s">
         <v>29</v>
@@ -14585,22 +14584,22 @@
         <v>24</v>
       </c>
       <c r="Q164" t="s">
+        <v>1245</v>
+      </c>
+      <c r="R164" t="s">
         <v>1246</v>
       </c>
-      <c r="R164" t="s">
+      <c r="S164" t="s">
         <v>1247</v>
-      </c>
-      <c r="S164" t="s">
-        <v>1248</v>
       </c>
       <c r="T164" t="s">
         <v>27</v>
       </c>
       <c r="U164" t="s">
+        <v>1248</v>
+      </c>
+      <c r="V164" t="s">
         <v>1249</v>
-      </c>
-      <c r="V164" t="s">
-        <v>1250</v>
       </c>
       <c r="W164" t="s">
         <v>280</v>
@@ -14611,19 +14610,19 @@
     </row>
     <row r="165" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C165" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D165" t="s">
         <v>1251</v>
       </c>
-      <c r="D165" t="s">
+      <c r="E165" t="s">
         <v>1252</v>
       </c>
-      <c r="E165" t="s">
+      <c r="F165" t="s">
         <v>1253</v>
       </c>
-      <c r="F165" t="s">
+      <c r="G165" t="s">
         <v>1254</v>
-      </c>
-      <c r="G165" t="s">
-        <v>1255</v>
       </c>
       <c r="H165" t="s">
         <v>25</v>
@@ -14638,7 +14637,7 @@
         <v>191</v>
       </c>
       <c r="L165" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="N165" t="s">
         <v>749</v>
@@ -14650,22 +14649,22 @@
         <v>24</v>
       </c>
       <c r="Q165" t="s">
+        <v>1245</v>
+      </c>
+      <c r="R165" t="s">
         <v>1246</v>
       </c>
-      <c r="R165" t="s">
+      <c r="S165" t="s">
         <v>1247</v>
-      </c>
-      <c r="S165" t="s">
-        <v>1248</v>
       </c>
       <c r="T165" t="s">
         <v>27</v>
       </c>
       <c r="U165" t="s">
+        <v>1248</v>
+      </c>
+      <c r="V165" t="s">
         <v>1249</v>
-      </c>
-      <c r="V165" t="s">
-        <v>1250</v>
       </c>
       <c r="W165" t="s">
         <v>312</v>
@@ -14676,19 +14675,19 @@
     </row>
     <row r="166" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C166" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D166" t="s">
         <v>1257</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166" t="s">
         <v>1258</v>
       </c>
-      <c r="E166" t="s">
+      <c r="F166" t="s">
         <v>1259</v>
       </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
         <v>1260</v>
-      </c>
-      <c r="G166" t="s">
-        <v>1261</v>
       </c>
       <c r="H166" t="s">
         <v>25</v>
@@ -14735,19 +14734,19 @@
     </row>
     <row r="167" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C167" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D167" t="s">
         <v>1262</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>1263</v>
       </c>
-      <c r="E167" t="s">
+      <c r="F167" t="s">
         <v>1264</v>
       </c>
-      <c r="F167" t="s">
+      <c r="G167" t="s">
         <v>1265</v>
-      </c>
-      <c r="G167" t="s">
-        <v>1266</v>
       </c>
       <c r="H167" t="s">
         <v>25</v>
@@ -14774,22 +14773,22 @@
         <v>24</v>
       </c>
       <c r="Q167" t="s">
+        <v>1266</v>
+      </c>
+      <c r="R167" t="s">
         <v>1267</v>
       </c>
-      <c r="R167" t="s">
+      <c r="S167" t="s">
         <v>1268</v>
-      </c>
-      <c r="S167" t="s">
-        <v>1269</v>
       </c>
       <c r="T167" t="s">
         <v>27</v>
       </c>
       <c r="U167" t="s">
+        <v>1269</v>
+      </c>
+      <c r="V167" t="s">
         <v>1270</v>
-      </c>
-      <c r="V167" t="s">
-        <v>1271</v>
       </c>
       <c r="W167" t="s">
         <v>280</v>
@@ -14800,16 +14799,16 @@
     </row>
     <row r="168" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C168" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D168" t="s">
         <v>1272</v>
       </c>
-      <c r="D168" t="s">
+      <c r="E168" t="s">
         <v>1273</v>
       </c>
-      <c r="E168" t="s">
+      <c r="F168" t="s">
         <v>1274</v>
-      </c>
-      <c r="F168" t="s">
-        <v>1275</v>
       </c>
       <c r="G168" t="s">
         <v>1062</v>
@@ -14839,22 +14838,22 @@
         <v>24</v>
       </c>
       <c r="Q168" t="s">
+        <v>1266</v>
+      </c>
+      <c r="R168" t="s">
         <v>1267</v>
       </c>
-      <c r="R168" t="s">
+      <c r="S168" t="s">
         <v>1268</v>
-      </c>
-      <c r="S168" t="s">
-        <v>1269</v>
       </c>
       <c r="T168" t="s">
         <v>27</v>
       </c>
       <c r="U168" t="s">
+        <v>1269</v>
+      </c>
+      <c r="V168" t="s">
         <v>1270</v>
-      </c>
-      <c r="V168" t="s">
-        <v>1271</v>
       </c>
       <c r="W168" t="s">
         <v>280</v>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCA48CC9-70F0-4837-A8C6-E869F554E594}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE644833-817B-474C-B719-314C1BA1D0CC}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3895,7 +3895,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -4204,7 +4206,7 @@
     <col min="4" max="4" width="34.83984375" customWidth="1"/>
     <col min="5" max="5" width="25.83984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="34.41796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.62890625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.62890625" customWidth="1"/>
     <col min="11" max="11" width="10.20703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.83984375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.41796875" bestFit="1" customWidth="1"/>
@@ -10969,7 +10971,7 @@
         <v>590</v>
       </c>
       <c r="G107" s="1">
-        <v>45934</v>
+        <v>46299</v>
       </c>
       <c r="H107" t="s">
         <v>29</v>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE644833-817B-474C-B719-314C1BA1D0CC}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA04839C-9C62-408A-80C9-90634B12F4E3}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3864,6 +3864,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3895,7 +3898,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3913,6 +3916,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA04839C-9C62-408A-80C9-90634B12F4E3}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4664BA18-2A8F-4986-89AC-9B33A0E47497}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3865,7 +3865,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -3898,7 +3898,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -10978,7 +10978,7 @@
         <v>590</v>
       </c>
       <c r="G107" s="1">
-        <v>46299</v>
+        <v>45934</v>
       </c>
       <c r="H107" t="s">
         <v>29</v>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4664BA18-2A8F-4986-89AC-9B33A0E47497}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC3AFE20-896E-43FB-986F-EDA48803379B}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3435" uniqueCount="1275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3436" uniqueCount="1275">
   <si>
     <t>SELECTION 1</t>
   </si>
@@ -3251,9 +3251,6 @@
     <t>11.02.2025</t>
   </si>
   <si>
-    <t>106</t>
-  </si>
-  <si>
     <t>77955</t>
   </si>
   <si>
@@ -3858,15 +3855,15 @@
   </si>
   <si>
     <t>TI*Aladin Royal Farm Narnia</t>
+  </si>
+  <si>
+    <t>04.10.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
-  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3896,11 +3893,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -10965,8 +10959,8 @@
       </c>
     </row>
     <row r="107" spans="3:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="C107" t="s">
-        <v>1072</v>
+      <c r="C107">
+        <v>6</v>
       </c>
       <c r="D107" t="s">
         <v>744</v>
@@ -10977,8 +10971,8 @@
       <c r="F107" t="s">
         <v>590</v>
       </c>
-      <c r="G107" s="1">
-        <v>45934</v>
+      <c r="G107" t="s">
+        <v>1274</v>
       </c>
       <c r="H107" t="s">
         <v>29</v>
@@ -11014,7 +11008,7 @@
         <v>126</v>
       </c>
       <c r="U107" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="V107" t="s">
         <v>594</v>
@@ -11025,10 +11019,10 @@
     </row>
     <row r="108" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C108" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D108" t="s">
         <v>1074</v>
-      </c>
-      <c r="D108" t="s">
-        <v>1075</v>
       </c>
       <c r="E108" t="s">
         <v>194</v>
@@ -11037,7 +11031,7 @@
         <v>595</v>
       </c>
       <c r="G108" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H108" t="s">
         <v>25</v>
@@ -11076,7 +11070,7 @@
         <v>27</v>
       </c>
       <c r="U108" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="V108" t="s">
         <v>198</v>
@@ -11090,10 +11084,10 @@
     </row>
     <row r="109" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C109" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D109" t="s">
         <v>1078</v>
-      </c>
-      <c r="D109" t="s">
-        <v>1079</v>
       </c>
       <c r="E109" t="s">
         <v>596</v>
@@ -11101,8 +11095,8 @@
       <c r="F109" t="s">
         <v>597</v>
       </c>
-      <c r="G109" s="1">
-        <v>45748</v>
+      <c r="G109" t="s">
+        <v>1079</v>
       </c>
       <c r="H109" t="s">
         <v>25</v>
@@ -11141,7 +11135,7 @@
         <v>27</v>
       </c>
       <c r="U109" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="V109" t="s">
         <v>601</v>
@@ -11155,10 +11149,10 @@
     </row>
     <row r="110" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C110" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D110" t="s">
         <v>1082</v>
-      </c>
-      <c r="D110" t="s">
-        <v>1083</v>
       </c>
       <c r="E110" t="s">
         <v>602</v>
@@ -11206,7 +11200,7 @@
         <v>27</v>
       </c>
       <c r="U110" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="V110" t="s">
         <v>198</v>
@@ -11220,10 +11214,10 @@
     </row>
     <row r="111" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C111" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D111" t="s">
         <v>1084</v>
-      </c>
-      <c r="D111" t="s">
-        <v>1085</v>
       </c>
       <c r="E111" t="s">
         <v>604</v>
@@ -11271,7 +11265,7 @@
         <v>27</v>
       </c>
       <c r="U111" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="V111" t="s">
         <v>198</v>
@@ -11285,10 +11279,10 @@
     </row>
     <row r="112" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C112" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D112" t="s">
         <v>1086</v>
-      </c>
-      <c r="D112" t="s">
-        <v>1087</v>
       </c>
       <c r="E112" t="s">
         <v>606</v>
@@ -11297,7 +11291,7 @@
         <v>607</v>
       </c>
       <c r="G112" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H112" t="s">
         <v>29</v>
@@ -11336,7 +11330,7 @@
         <v>27</v>
       </c>
       <c r="U112" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="V112" t="s">
         <v>601</v>
@@ -11350,10 +11344,10 @@
     </row>
     <row r="113" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C113" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D113" t="s">
         <v>1089</v>
-      </c>
-      <c r="D113" t="s">
-        <v>1090</v>
       </c>
       <c r="E113" t="s">
         <v>608</v>
@@ -11362,7 +11356,7 @@
         <v>609</v>
       </c>
       <c r="G113" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H113" t="s">
         <v>29</v>
@@ -11401,7 +11395,7 @@
         <v>27</v>
       </c>
       <c r="U113" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="V113" t="s">
         <v>601</v>
@@ -11415,10 +11409,10 @@
     </row>
     <row r="114" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C114" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D114" t="s">
         <v>1091</v>
-      </c>
-      <c r="D114" t="s">
-        <v>1092</v>
       </c>
       <c r="E114" t="s">
         <v>610</v>
@@ -11427,7 +11421,7 @@
         <v>611</v>
       </c>
       <c r="G114" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H114" t="s">
         <v>25</v>
@@ -11466,7 +11460,7 @@
         <v>27</v>
       </c>
       <c r="U114" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="V114" t="s">
         <v>601</v>
@@ -11480,10 +11474,10 @@
     </row>
     <row r="115" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C115" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D115" t="s">
         <v>1093</v>
-      </c>
-      <c r="D115" t="s">
-        <v>1094</v>
       </c>
       <c r="E115" t="s">
         <v>612</v>
@@ -11492,7 +11486,7 @@
         <v>613</v>
       </c>
       <c r="G115" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H115" t="s">
         <v>29</v>
@@ -11528,7 +11522,7 @@
         <v>27</v>
       </c>
       <c r="U115" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="V115" t="s">
         <v>617</v>
@@ -11539,10 +11533,10 @@
     </row>
     <row r="116" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C116" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D116" t="s">
         <v>1097</v>
-      </c>
-      <c r="D116" t="s">
-        <v>1098</v>
       </c>
       <c r="E116" t="s">
         <v>200</v>
@@ -11551,7 +11545,7 @@
         <v>618</v>
       </c>
       <c r="G116" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H116" t="s">
         <v>29</v>
@@ -11593,7 +11587,7 @@
         <v>27</v>
       </c>
       <c r="U116" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="V116" t="s">
         <v>204</v>
@@ -11607,10 +11601,10 @@
     </row>
     <row r="117" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C117" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D117" t="s">
         <v>1101</v>
-      </c>
-      <c r="D117" t="s">
-        <v>1102</v>
       </c>
       <c r="E117" t="s">
         <v>205</v>
@@ -11619,7 +11613,7 @@
         <v>619</v>
       </c>
       <c r="G117" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H117" t="s">
         <v>29</v>
@@ -11658,7 +11652,7 @@
         <v>27</v>
       </c>
       <c r="U117" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="V117" t="s">
         <v>204</v>
@@ -11672,10 +11666,10 @@
     </row>
     <row r="118" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C118" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D118" t="s">
         <v>1104</v>
-      </c>
-      <c r="D118" t="s">
-        <v>1105</v>
       </c>
       <c r="E118" t="s">
         <v>620</v>
@@ -11723,7 +11717,7 @@
         <v>27</v>
       </c>
       <c r="U118" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="V118" t="s">
         <v>204</v>
@@ -11737,10 +11731,10 @@
     </row>
     <row r="119" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C119" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D119" t="s">
         <v>1106</v>
-      </c>
-      <c r="D119" t="s">
-        <v>1107</v>
       </c>
       <c r="E119" t="s">
         <v>623</v>
@@ -11749,7 +11743,7 @@
         <v>624</v>
       </c>
       <c r="G119" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H119" t="s">
         <v>29</v>
@@ -11788,7 +11782,7 @@
         <v>27</v>
       </c>
       <c r="U119" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="V119" t="s">
         <v>215</v>
@@ -11802,10 +11796,10 @@
     </row>
     <row r="120" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C120" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D120" t="s">
         <v>1110</v>
-      </c>
-      <c r="D120" t="s">
-        <v>1111</v>
       </c>
       <c r="E120" t="s">
         <v>625</v>
@@ -11814,7 +11808,7 @@
         <v>626</v>
       </c>
       <c r="G120" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H120" t="s">
         <v>29</v>
@@ -11850,7 +11844,7 @@
         <v>27</v>
       </c>
       <c r="U120" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="V120" t="s">
         <v>630</v>
@@ -11861,10 +11855,10 @@
     </row>
     <row r="121" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C121" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D121" t="s">
         <v>1114</v>
-      </c>
-      <c r="D121" t="s">
-        <v>1115</v>
       </c>
       <c r="E121" t="s">
         <v>631</v>
@@ -11873,7 +11867,7 @@
         <v>632</v>
       </c>
       <c r="G121" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H121" t="s">
         <v>29</v>
@@ -11909,7 +11903,7 @@
         <v>27</v>
       </c>
       <c r="U121" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="V121" t="s">
         <v>630</v>
@@ -11920,10 +11914,10 @@
     </row>
     <row r="122" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C122" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D122" t="s">
         <v>1117</v>
-      </c>
-      <c r="D122" t="s">
-        <v>1118</v>
       </c>
       <c r="E122" t="s">
         <v>633</v>
@@ -11971,7 +11965,7 @@
         <v>27</v>
       </c>
       <c r="U122" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="V122" t="s">
         <v>215</v>
@@ -11985,10 +11979,10 @@
     </row>
     <row r="123" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C123" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D123" t="s">
         <v>1119</v>
-      </c>
-      <c r="D123" t="s">
-        <v>1120</v>
       </c>
       <c r="E123" t="s">
         <v>635</v>
@@ -11997,7 +11991,7 @@
         <v>636</v>
       </c>
       <c r="G123" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H123" t="s">
         <v>29</v>
@@ -12033,7 +12027,7 @@
         <v>27</v>
       </c>
       <c r="U123" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="V123" t="s">
         <v>630</v>
@@ -12044,7 +12038,7 @@
     </row>
     <row r="124" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C124" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D124" t="s">
         <v>744</v>
@@ -12092,7 +12086,7 @@
         <v>126</v>
       </c>
       <c r="U124" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="V124" t="s">
         <v>594</v>
@@ -12103,10 +12097,10 @@
     </row>
     <row r="125" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C125" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D125" t="s">
         <v>1122</v>
-      </c>
-      <c r="D125" t="s">
-        <v>1123</v>
       </c>
       <c r="E125" t="s">
         <v>640</v>
@@ -12115,7 +12109,7 @@
         <v>641</v>
       </c>
       <c r="G125" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H125" t="s">
         <v>25</v>
@@ -12151,7 +12145,7 @@
         <v>126</v>
       </c>
       <c r="U125" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="V125" t="s">
         <v>646</v>
@@ -12162,10 +12156,10 @@
     </row>
     <row r="126" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C126" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D126" t="s">
         <v>1126</v>
-      </c>
-      <c r="D126" t="s">
-        <v>1127</v>
       </c>
       <c r="E126" t="s">
         <v>647</v>
@@ -12210,7 +12204,7 @@
         <v>126</v>
       </c>
       <c r="U126" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="V126" t="s">
         <v>646</v>
@@ -12221,10 +12215,10 @@
     </row>
     <row r="127" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C127" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D127" t="s">
         <v>1128</v>
-      </c>
-      <c r="D127" t="s">
-        <v>1129</v>
       </c>
       <c r="E127" t="s">
         <v>649</v>
@@ -12233,7 +12227,7 @@
         <v>650</v>
       </c>
       <c r="G127" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H127" t="s">
         <v>25</v>
@@ -12269,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="U127" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="V127" t="s">
         <v>220</v>
@@ -12283,10 +12277,10 @@
     </row>
     <row r="128" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C128" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D128" t="s">
         <v>1132</v>
-      </c>
-      <c r="D128" t="s">
-        <v>1133</v>
       </c>
       <c r="E128" t="s">
         <v>225</v>
@@ -12331,7 +12325,7 @@
         <v>27</v>
       </c>
       <c r="U128" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="V128" t="s">
         <v>224</v>
@@ -12345,10 +12339,10 @@
     </row>
     <row r="129" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C129" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D129" t="s">
         <v>1135</v>
-      </c>
-      <c r="D129" t="s">
-        <v>1136</v>
       </c>
       <c r="E129" t="s">
         <v>226</v>
@@ -12357,7 +12351,7 @@
         <v>652</v>
       </c>
       <c r="G129" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H129" t="s">
         <v>29</v>
@@ -12393,7 +12387,7 @@
         <v>27</v>
       </c>
       <c r="U129" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="V129" t="s">
         <v>220</v>
@@ -12407,10 +12401,10 @@
     </row>
     <row r="130" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C130" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D130" t="s">
         <v>1138</v>
-      </c>
-      <c r="D130" t="s">
-        <v>1139</v>
       </c>
       <c r="E130" t="s">
         <v>653</v>
@@ -12455,7 +12449,7 @@
         <v>27</v>
       </c>
       <c r="U130" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="V130" t="s">
         <v>659</v>
@@ -12466,10 +12460,10 @@
     </row>
     <row r="131" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C131" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D131" t="s">
         <v>1141</v>
-      </c>
-      <c r="D131" t="s">
-        <v>1142</v>
       </c>
       <c r="E131" t="s">
         <v>660</v>
@@ -12478,7 +12472,7 @@
         <v>661</v>
       </c>
       <c r="G131" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H131" t="s">
         <v>25</v>
@@ -12514,7 +12508,7 @@
         <v>27</v>
       </c>
       <c r="U131" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="V131" t="s">
         <v>659</v>
@@ -12525,10 +12519,10 @@
     </row>
     <row r="132" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C132" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D132" t="s">
         <v>1144</v>
-      </c>
-      <c r="D132" t="s">
-        <v>1145</v>
       </c>
       <c r="E132" t="s">
         <v>232</v>
@@ -12537,7 +12531,7 @@
         <v>662</v>
       </c>
       <c r="G132" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H132" t="s">
         <v>29</v>
@@ -12576,7 +12570,7 @@
         <v>27</v>
       </c>
       <c r="U132" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="V132" t="s">
         <v>231</v>
@@ -12590,10 +12584,10 @@
     </row>
     <row r="133" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C133" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D133" t="s">
         <v>1148</v>
-      </c>
-      <c r="D133" t="s">
-        <v>1149</v>
       </c>
       <c r="E133" t="s">
         <v>663</v>
@@ -12602,7 +12596,7 @@
         <v>664</v>
       </c>
       <c r="G133" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H133" t="s">
         <v>29</v>
@@ -12638,7 +12632,7 @@
         <v>27</v>
       </c>
       <c r="U133" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="V133" t="s">
         <v>220</v>
@@ -12652,10 +12646,10 @@
     </row>
     <row r="134" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C134" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D134" t="s">
         <v>1151</v>
-      </c>
-      <c r="D134" t="s">
-        <v>1152</v>
       </c>
       <c r="E134" t="s">
         <v>665</v>
@@ -12664,7 +12658,7 @@
         <v>666</v>
       </c>
       <c r="G134" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H134" t="s">
         <v>25</v>
@@ -12703,7 +12697,7 @@
         <v>27</v>
       </c>
       <c r="U134" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="V134" t="s">
         <v>220</v>
@@ -12717,10 +12711,10 @@
     </row>
     <row r="135" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C135" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D135" t="s">
         <v>1154</v>
-      </c>
-      <c r="D135" t="s">
-        <v>1155</v>
       </c>
       <c r="E135" t="s">
         <v>667</v>
@@ -12729,7 +12723,7 @@
         <v>668</v>
       </c>
       <c r="G135" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H135" t="s">
         <v>25</v>
@@ -12779,10 +12773,10 @@
     </row>
     <row r="136" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C136" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D136" t="s">
         <v>1156</v>
-      </c>
-      <c r="D136" t="s">
-        <v>1157</v>
       </c>
       <c r="E136" t="s">
         <v>673</v>
@@ -12791,7 +12785,7 @@
         <v>674</v>
       </c>
       <c r="G136" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H136" t="s">
         <v>25</v>
@@ -12844,10 +12838,10 @@
     </row>
     <row r="137" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C137" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D137" t="s">
         <v>1159</v>
-      </c>
-      <c r="D137" t="s">
-        <v>1160</v>
       </c>
       <c r="E137" t="s">
         <v>675</v>
@@ -12892,7 +12886,7 @@
         <v>27</v>
       </c>
       <c r="U137" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="V137" t="s">
         <v>220</v>
@@ -12906,10 +12900,10 @@
     </row>
     <row r="138" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C138" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D138" t="s">
         <v>1161</v>
-      </c>
-      <c r="D138" t="s">
-        <v>1162</v>
       </c>
       <c r="E138" t="s">
         <v>677</v>
@@ -12954,7 +12948,7 @@
         <v>27</v>
       </c>
       <c r="U138" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="V138" t="s">
         <v>220</v>
@@ -12968,10 +12962,10 @@
     </row>
     <row r="139" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C139" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D139" t="s">
         <v>1163</v>
-      </c>
-      <c r="D139" t="s">
-        <v>1164</v>
       </c>
       <c r="E139" t="s">
         <v>679</v>
@@ -12980,7 +12974,7 @@
         <v>680</v>
       </c>
       <c r="G139" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H139" t="s">
         <v>29</v>
@@ -13019,7 +13013,7 @@
         <v>27</v>
       </c>
       <c r="U139" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="V139" t="s">
         <v>237</v>
@@ -13033,10 +13027,10 @@
     </row>
     <row r="140" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C140" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D140" t="s">
         <v>1167</v>
-      </c>
-      <c r="D140" t="s">
-        <v>1168</v>
       </c>
       <c r="E140" t="s">
         <v>681</v>
@@ -13045,7 +13039,7 @@
         <v>682</v>
       </c>
       <c r="G140" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H140" t="s">
         <v>25</v>
@@ -13084,7 +13078,7 @@
         <v>687</v>
       </c>
       <c r="U140" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="V140" t="s">
         <v>688</v>
@@ -13098,10 +13092,10 @@
     </row>
     <row r="141" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C141" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D141" t="s">
         <v>1171</v>
-      </c>
-      <c r="D141" t="s">
-        <v>1172</v>
       </c>
       <c r="E141" t="s">
         <v>689</v>
@@ -13110,7 +13104,7 @@
         <v>690</v>
       </c>
       <c r="G141" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H141" t="s">
         <v>25</v>
@@ -13149,7 +13143,7 @@
         <v>126</v>
       </c>
       <c r="U141" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="V141" t="s">
         <v>250</v>
@@ -13160,7 +13154,7 @@
     </row>
     <row r="142" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C142" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="D142" t="s">
         <v>691</v>
@@ -13211,7 +13205,7 @@
         <v>126</v>
       </c>
       <c r="U142" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="V142" t="s">
         <v>242</v>
@@ -13225,7 +13219,7 @@
     </row>
     <row r="143" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C143" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D143" t="s">
         <v>243</v>
@@ -13237,7 +13231,7 @@
         <v>245</v>
       </c>
       <c r="G143" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H143" t="s">
         <v>25</v>
@@ -13276,7 +13270,7 @@
         <v>126</v>
       </c>
       <c r="U143" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="V143" t="s">
         <v>242</v>
@@ -13290,10 +13284,10 @@
     </row>
     <row r="144" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C144" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D144" t="s">
         <v>1179</v>
-      </c>
-      <c r="D144" t="s">
-        <v>1180</v>
       </c>
       <c r="E144" t="s">
         <v>695</v>
@@ -13302,7 +13296,7 @@
         <v>696</v>
       </c>
       <c r="G144" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H144" t="s">
         <v>25</v>
@@ -13338,7 +13332,7 @@
         <v>126</v>
       </c>
       <c r="U144" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="V144" t="s">
         <v>250</v>
@@ -13349,10 +13343,10 @@
     </row>
     <row r="145" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C145" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D145" t="s">
         <v>1182</v>
-      </c>
-      <c r="D145" t="s">
-        <v>1183</v>
       </c>
       <c r="E145" t="s">
         <v>252</v>
@@ -13361,7 +13355,7 @@
         <v>697</v>
       </c>
       <c r="G145" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H145" t="s">
         <v>25</v>
@@ -13397,7 +13391,7 @@
         <v>27</v>
       </c>
       <c r="U145" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="V145" t="s">
         <v>256</v>
@@ -13408,10 +13402,10 @@
     </row>
     <row r="146" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C146" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D146" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="E146" t="s">
         <v>698</v>
@@ -13420,7 +13414,7 @@
         <v>699</v>
       </c>
       <c r="G146" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H146" t="s">
         <v>29</v>
@@ -13456,7 +13450,7 @@
         <v>126</v>
       </c>
       <c r="U146" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="V146" t="s">
         <v>250</v>
@@ -13467,7 +13461,7 @@
     </row>
     <row r="147" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C147" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D147" t="s">
         <v>701</v>
@@ -13479,7 +13473,7 @@
         <v>703</v>
       </c>
       <c r="G147" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H147" t="s">
         <v>29</v>
@@ -13518,7 +13512,7 @@
         <v>126</v>
       </c>
       <c r="U147" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="V147" t="s">
         <v>242</v>
@@ -13532,10 +13526,10 @@
     </row>
     <row r="148" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C148" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D148" t="s">
         <v>1189</v>
-      </c>
-      <c r="D148" t="s">
-        <v>1190</v>
       </c>
       <c r="E148" t="s">
         <v>704</v>
@@ -13544,7 +13538,7 @@
         <v>705</v>
       </c>
       <c r="G148" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H148" t="s">
         <v>25</v>
@@ -13580,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="U148" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="V148" t="s">
         <v>709</v>
@@ -13591,10 +13585,10 @@
     </row>
     <row r="149" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C149" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D149" t="s">
         <v>1193</v>
-      </c>
-      <c r="D149" t="s">
-        <v>1194</v>
       </c>
       <c r="E149" t="s">
         <v>710</v>
@@ -13603,7 +13597,7 @@
         <v>711</v>
       </c>
       <c r="G149" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H149" t="s">
         <v>29</v>
@@ -13639,7 +13633,7 @@
         <v>27</v>
       </c>
       <c r="U149" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="V149" t="s">
         <v>709</v>
@@ -13650,10 +13644,10 @@
     </row>
     <row r="150" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C150" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D150" t="s">
         <v>1196</v>
-      </c>
-      <c r="D150" t="s">
-        <v>1197</v>
       </c>
       <c r="E150" t="s">
         <v>258</v>
@@ -13662,7 +13656,7 @@
         <v>712</v>
       </c>
       <c r="G150" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H150" t="s">
         <v>29</v>
@@ -13701,7 +13695,7 @@
         <v>126</v>
       </c>
       <c r="U150" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="V150" t="s">
         <v>262</v>
@@ -13715,10 +13709,10 @@
     </row>
     <row r="151" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C151" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D151" t="s">
         <v>1200</v>
-      </c>
-      <c r="D151" t="s">
-        <v>1201</v>
       </c>
       <c r="E151" t="s">
         <v>263</v>
@@ -13727,7 +13721,7 @@
         <v>713</v>
       </c>
       <c r="G151" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H151" t="s">
         <v>25</v>
@@ -13766,7 +13760,7 @@
         <v>126</v>
       </c>
       <c r="U151" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="V151" t="s">
         <v>262</v>
@@ -13780,10 +13774,10 @@
     </row>
     <row r="152" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C152" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D152" t="s">
         <v>1203</v>
-      </c>
-      <c r="D152" t="s">
-        <v>1204</v>
       </c>
       <c r="E152" t="s">
         <v>265</v>
@@ -13792,7 +13786,7 @@
         <v>714</v>
       </c>
       <c r="G152" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H152" t="s">
         <v>29</v>
@@ -13831,7 +13825,7 @@
         <v>126</v>
       </c>
       <c r="U152" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="V152" t="s">
         <v>262</v>
@@ -13845,10 +13839,10 @@
     </row>
     <row r="153" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C153" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D153" t="s">
         <v>1205</v>
-      </c>
-      <c r="D153" t="s">
-        <v>1206</v>
       </c>
       <c r="E153" t="s">
         <v>715</v>
@@ -13857,7 +13851,7 @@
         <v>716</v>
       </c>
       <c r="G153" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H153" t="s">
         <v>25</v>
@@ -13896,7 +13890,7 @@
         <v>126</v>
       </c>
       <c r="U153" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="V153" t="s">
         <v>262</v>
@@ -13910,10 +13904,10 @@
     </row>
     <row r="154" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C154" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D154" t="s">
         <v>1208</v>
-      </c>
-      <c r="D154" t="s">
-        <v>1209</v>
       </c>
       <c r="E154" t="s">
         <v>717</v>
@@ -13922,7 +13916,7 @@
         <v>718</v>
       </c>
       <c r="G154" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H154" t="s">
         <v>29</v>
@@ -13961,7 +13955,7 @@
         <v>126</v>
       </c>
       <c r="U154" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="V154" t="s">
         <v>262</v>
@@ -13975,10 +13969,10 @@
     </row>
     <row r="155" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C155" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D155" t="s">
         <v>1211</v>
-      </c>
-      <c r="D155" t="s">
-        <v>1212</v>
       </c>
       <c r="E155" t="s">
         <v>719</v>
@@ -13987,7 +13981,7 @@
         <v>720</v>
       </c>
       <c r="G155" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H155" t="s">
         <v>29</v>
@@ -14026,7 +14020,7 @@
         <v>27</v>
       </c>
       <c r="U155" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="V155" t="s">
         <v>722</v>
@@ -14040,10 +14034,10 @@
     </row>
     <row r="156" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C156" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D156" t="s">
         <v>1215</v>
-      </c>
-      <c r="D156" t="s">
-        <v>1216</v>
       </c>
       <c r="E156" t="s">
         <v>723</v>
@@ -14052,7 +14046,7 @@
         <v>724</v>
       </c>
       <c r="G156" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H156" t="s">
         <v>29</v>
@@ -14091,7 +14085,7 @@
         <v>27</v>
       </c>
       <c r="U156" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="V156" t="s">
         <v>722</v>
@@ -14105,10 +14099,10 @@
     </row>
     <row r="157" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C157" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D157" t="s">
         <v>1218</v>
-      </c>
-      <c r="D157" t="s">
-        <v>1219</v>
       </c>
       <c r="E157" t="s">
         <v>725</v>
@@ -14117,7 +14111,7 @@
         <v>726</v>
       </c>
       <c r="G157" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H157" t="s">
         <v>29</v>
@@ -14156,7 +14150,7 @@
         <v>126</v>
       </c>
       <c r="U157" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="V157" t="s">
         <v>262</v>
@@ -14170,10 +14164,10 @@
     </row>
     <row r="158" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C158" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D158" t="s">
         <v>1221</v>
-      </c>
-      <c r="D158" t="s">
-        <v>1222</v>
       </c>
       <c r="E158" t="s">
         <v>727</v>
@@ -14182,7 +14176,7 @@
         <v>728</v>
       </c>
       <c r="G158" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H158" t="s">
         <v>25</v>
@@ -14221,7 +14215,7 @@
         <v>27</v>
       </c>
       <c r="U158" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="V158" t="s">
         <v>722</v>
@@ -14235,10 +14229,10 @@
     </row>
     <row r="159" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C159" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D159" t="s">
         <v>1224</v>
-      </c>
-      <c r="D159" t="s">
-        <v>1225</v>
       </c>
       <c r="E159" t="s">
         <v>729</v>
@@ -14247,7 +14241,7 @@
         <v>730</v>
       </c>
       <c r="G159" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H159" t="s">
         <v>25</v>
@@ -14286,7 +14280,7 @@
         <v>27</v>
       </c>
       <c r="U159" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="V159" t="s">
         <v>722</v>
@@ -14300,10 +14294,10 @@
     </row>
     <row r="160" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C160" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D160" t="s">
         <v>1227</v>
-      </c>
-      <c r="D160" t="s">
-        <v>1228</v>
       </c>
       <c r="E160" t="s">
         <v>731</v>
@@ -14312,7 +14306,7 @@
         <v>732</v>
       </c>
       <c r="G160" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H160" t="s">
         <v>29</v>
@@ -14351,7 +14345,7 @@
         <v>27</v>
       </c>
       <c r="U160" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="V160" t="s">
         <v>722</v>
@@ -14365,10 +14359,10 @@
     </row>
     <row r="161" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C161" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D161" t="s">
         <v>1230</v>
-      </c>
-      <c r="D161" t="s">
-        <v>1231</v>
       </c>
       <c r="E161" t="s">
         <v>733</v>
@@ -14377,7 +14371,7 @@
         <v>734</v>
       </c>
       <c r="G161" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H161" t="s">
         <v>29</v>
@@ -14416,7 +14410,7 @@
         <v>27</v>
       </c>
       <c r="U161" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="V161" t="s">
         <v>722</v>
@@ -14430,10 +14424,10 @@
     </row>
     <row r="162" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C162" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D162" t="s">
         <v>1233</v>
-      </c>
-      <c r="D162" t="s">
-        <v>1234</v>
       </c>
       <c r="E162" t="s">
         <v>735</v>
@@ -14442,7 +14436,7 @@
         <v>736</v>
       </c>
       <c r="G162" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H162" t="s">
         <v>25</v>
@@ -14481,7 +14475,7 @@
         <v>27</v>
       </c>
       <c r="U162" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="V162" t="s">
         <v>740</v>
@@ -14495,10 +14489,10 @@
     </row>
     <row r="163" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C163" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D163" t="s">
         <v>1237</v>
-      </c>
-      <c r="D163" t="s">
-        <v>1238</v>
       </c>
       <c r="E163" t="s">
         <v>269</v>
@@ -14507,7 +14501,7 @@
         <v>270</v>
       </c>
       <c r="G163" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H163" t="s">
         <v>29</v>
@@ -14543,7 +14537,7 @@
         <v>27</v>
       </c>
       <c r="U163" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="V163" t="s">
         <v>256</v>
@@ -14554,19 +14548,19 @@
     </row>
     <row r="164" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C164" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D164" t="s">
         <v>1240</v>
       </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
         <v>1241</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
         <v>1242</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
         <v>1243</v>
-      </c>
-      <c r="G164" t="s">
-        <v>1244</v>
       </c>
       <c r="H164" t="s">
         <v>29</v>
@@ -14593,22 +14587,22 @@
         <v>24</v>
       </c>
       <c r="Q164" t="s">
+        <v>1244</v>
+      </c>
+      <c r="R164" t="s">
         <v>1245</v>
       </c>
-      <c r="R164" t="s">
+      <c r="S164" t="s">
         <v>1246</v>
-      </c>
-      <c r="S164" t="s">
-        <v>1247</v>
       </c>
       <c r="T164" t="s">
         <v>27</v>
       </c>
       <c r="U164" t="s">
+        <v>1247</v>
+      </c>
+      <c r="V164" t="s">
         <v>1248</v>
-      </c>
-      <c r="V164" t="s">
-        <v>1249</v>
       </c>
       <c r="W164" t="s">
         <v>280</v>
@@ -14619,19 +14613,19 @@
     </row>
     <row r="165" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C165" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D165" t="s">
         <v>1250</v>
       </c>
-      <c r="D165" t="s">
+      <c r="E165" t="s">
         <v>1251</v>
       </c>
-      <c r="E165" t="s">
+      <c r="F165" t="s">
         <v>1252</v>
       </c>
-      <c r="F165" t="s">
+      <c r="G165" t="s">
         <v>1253</v>
-      </c>
-      <c r="G165" t="s">
-        <v>1254</v>
       </c>
       <c r="H165" t="s">
         <v>25</v>
@@ -14646,7 +14640,7 @@
         <v>191</v>
       </c>
       <c r="L165" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="N165" t="s">
         <v>749</v>
@@ -14658,22 +14652,22 @@
         <v>24</v>
       </c>
       <c r="Q165" t="s">
+        <v>1244</v>
+      </c>
+      <c r="R165" t="s">
         <v>1245</v>
       </c>
-      <c r="R165" t="s">
+      <c r="S165" t="s">
         <v>1246</v>
-      </c>
-      <c r="S165" t="s">
-        <v>1247</v>
       </c>
       <c r="T165" t="s">
         <v>27</v>
       </c>
       <c r="U165" t="s">
+        <v>1247</v>
+      </c>
+      <c r="V165" t="s">
         <v>1248</v>
-      </c>
-      <c r="V165" t="s">
-        <v>1249</v>
       </c>
       <c r="W165" t="s">
         <v>312</v>
@@ -14684,19 +14678,19 @@
     </row>
     <row r="166" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C166" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D166" t="s">
         <v>1256</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166" t="s">
         <v>1257</v>
       </c>
-      <c r="E166" t="s">
+      <c r="F166" t="s">
         <v>1258</v>
       </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
         <v>1259</v>
-      </c>
-      <c r="G166" t="s">
-        <v>1260</v>
       </c>
       <c r="H166" t="s">
         <v>25</v>
@@ -14743,19 +14737,19 @@
     </row>
     <row r="167" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C167" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D167" t="s">
         <v>1261</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>1262</v>
       </c>
-      <c r="E167" t="s">
+      <c r="F167" t="s">
         <v>1263</v>
       </c>
-      <c r="F167" t="s">
+      <c r="G167" t="s">
         <v>1264</v>
-      </c>
-      <c r="G167" t="s">
-        <v>1265</v>
       </c>
       <c r="H167" t="s">
         <v>25</v>
@@ -14782,22 +14776,22 @@
         <v>24</v>
       </c>
       <c r="Q167" t="s">
+        <v>1265</v>
+      </c>
+      <c r="R167" t="s">
         <v>1266</v>
       </c>
-      <c r="R167" t="s">
+      <c r="S167" t="s">
         <v>1267</v>
-      </c>
-      <c r="S167" t="s">
-        <v>1268</v>
       </c>
       <c r="T167" t="s">
         <v>27</v>
       </c>
       <c r="U167" t="s">
+        <v>1268</v>
+      </c>
+      <c r="V167" t="s">
         <v>1269</v>
-      </c>
-      <c r="V167" t="s">
-        <v>1270</v>
       </c>
       <c r="W167" t="s">
         <v>280</v>
@@ -14808,16 +14802,16 @@
     </row>
     <row r="168" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C168" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D168" t="s">
         <v>1271</v>
       </c>
-      <c r="D168" t="s">
+      <c r="E168" t="s">
         <v>1272</v>
       </c>
-      <c r="E168" t="s">
+      <c r="F168" t="s">
         <v>1273</v>
-      </c>
-      <c r="F168" t="s">
-        <v>1274</v>
       </c>
       <c r="G168" t="s">
         <v>1062</v>
@@ -14847,22 +14841,22 @@
         <v>24</v>
       </c>
       <c r="Q168" t="s">
+        <v>1265</v>
+      </c>
+      <c r="R168" t="s">
         <v>1266</v>
       </c>
-      <c r="R168" t="s">
+      <c r="S168" t="s">
         <v>1267</v>
-      </c>
-      <c r="S168" t="s">
-        <v>1268</v>
       </c>
       <c r="T168" t="s">
         <v>27</v>
       </c>
       <c r="U168" t="s">
+        <v>1268</v>
+      </c>
+      <c r="V168" t="s">
         <v>1269</v>
-      </c>
-      <c r="V168" t="s">
-        <v>1270</v>
       </c>
       <c r="W168" t="s">
         <v>280</v>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC3AFE20-896E-43FB-986F-EDA48803379B}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98C5C466-0475-4B4D-8CB1-1D623D273683}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3436" uniqueCount="1275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3437" uniqueCount="1276">
   <si>
     <t>SELECTION 1</t>
   </si>
@@ -3858,6 +3858,9 @@
   </si>
   <si>
     <t>04.10.2025</t>
+  </si>
+  <si>
+    <t>106</t>
   </si>
 </sst>
 </file>
@@ -10959,8 +10962,8 @@
       </c>
     </row>
     <row r="107" spans="3:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="C107">
-        <v>6</v>
+      <c r="C107" t="s">
+        <v>1275</v>
       </c>
       <c r="D107" t="s">
         <v>744</v>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98C5C466-0475-4B4D-8CB1-1D623D273683}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C2E1D0C-3107-46A5-ABC0-2539A30F1883}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3437" uniqueCount="1276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3446" uniqueCount="1276">
   <si>
     <t>SELECTION 1</t>
   </si>
@@ -4296,6 +4296,9 @@
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
       <c r="C2" t="s">
         <v>741</v>
       </c>
@@ -4426,6 +4429,9 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
       <c r="C4" t="s">
         <v>751</v>
       </c>
@@ -4556,6 +4562,9 @@
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
       <c r="C6" t="s">
         <v>745</v>
       </c>
@@ -4686,6 +4695,9 @@
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
       <c r="C8" t="s">
         <v>762</v>
       </c>
@@ -4816,6 +4828,9 @@
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
       <c r="C10" t="s">
         <v>749</v>
       </c>
@@ -4946,6 +4961,9 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
       <c r="C12" t="s">
         <v>767</v>
       </c>
@@ -5064,6 +5082,9 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
       <c r="C14" t="s">
         <v>776</v>
       </c>
@@ -5188,6 +5209,9 @@
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
       <c r="C16" t="s">
         <v>783</v>
       </c>
@@ -5252,7 +5276,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C17" t="s">
         <v>787</v>
       </c>
@@ -5317,7 +5341,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
       <c r="C18" t="s">
         <v>789</v>
       </c>
@@ -5376,7 +5403,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C19" t="s">
         <v>793</v>
       </c>
@@ -5435,7 +5462,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C20" t="s">
         <v>797</v>
       </c>
@@ -5497,7 +5524,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C21" t="s">
         <v>800</v>
       </c>
@@ -5556,7 +5583,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C22" t="s">
         <v>803</v>
       </c>
@@ -5624,7 +5651,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C23" t="s">
         <v>807</v>
       </c>
@@ -5683,7 +5710,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C24" t="s">
         <v>809</v>
       </c>
@@ -5742,7 +5769,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C25" t="s">
         <v>812</v>
       </c>
@@ -5801,7 +5828,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C26" t="s">
         <v>815</v>
       </c>
@@ -5860,7 +5887,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C27" t="s">
         <v>819</v>
       </c>
@@ -5919,7 +5946,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C28" t="s">
         <v>822</v>
       </c>
@@ -5984,7 +6011,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C29" t="s">
         <v>826</v>
       </c>
@@ -6049,7 +6076,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C30" t="s">
         <v>830</v>
       </c>
@@ -6114,7 +6141,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C31" t="s">
         <v>834</v>
       </c>
@@ -6179,7 +6206,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C32" t="s">
         <v>838</v>
       </c>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C2E1D0C-3107-46A5-ABC0-2539A30F1883}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{642852FB-CE0F-4F8C-9C47-0DBDB6410E5F}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3446" uniqueCount="1276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3437" uniqueCount="1276">
   <si>
     <t>SELECTION 1</t>
   </si>
@@ -4296,9 +4296,6 @@
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
       <c r="C2" t="s">
         <v>741</v>
       </c>
@@ -4429,9 +4426,6 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
       <c r="C4" t="s">
         <v>751</v>
       </c>
@@ -4562,9 +4556,6 @@
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
       <c r="C6" t="s">
         <v>745</v>
       </c>
@@ -4695,9 +4686,6 @@
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
       <c r="C8" t="s">
         <v>762</v>
       </c>
@@ -4828,9 +4816,6 @@
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
       <c r="C10" t="s">
         <v>749</v>
       </c>
@@ -4961,9 +4946,6 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
       <c r="C12" t="s">
         <v>767</v>
       </c>
@@ -5082,9 +5064,6 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
       <c r="C14" t="s">
         <v>776</v>
       </c>
@@ -5209,9 +5188,6 @@
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
       <c r="C16" t="s">
         <v>783</v>
       </c>
@@ -5276,7 +5252,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C17" t="s">
         <v>787</v>
       </c>
@@ -5341,10 +5317,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C18" t="s">
         <v>789</v>
       </c>
@@ -5403,7 +5376,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C19" t="s">
         <v>793</v>
       </c>
@@ -5462,7 +5435,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C20" t="s">
         <v>797</v>
       </c>
@@ -5524,7 +5497,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C21" t="s">
         <v>800</v>
       </c>
@@ -5583,7 +5556,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C22" t="s">
         <v>803</v>
       </c>
@@ -5651,7 +5624,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C23" t="s">
         <v>807</v>
       </c>
@@ -5710,7 +5683,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C24" t="s">
         <v>809</v>
       </c>
@@ -5769,7 +5742,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C25" t="s">
         <v>812</v>
       </c>
@@ -5828,7 +5801,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C26" t="s">
         <v>815</v>
       </c>
@@ -5887,7 +5860,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C27" t="s">
         <v>819</v>
       </c>
@@ -5946,7 +5919,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C28" t="s">
         <v>822</v>
       </c>
@@ -6011,7 +5984,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C29" t="s">
         <v>826</v>
       </c>
@@ -6076,7 +6049,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C30" t="s">
         <v>830</v>
       </c>
@@ -6141,7 +6114,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C31" t="s">
         <v>834</v>
       </c>
@@ -6206,7 +6179,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C32" t="s">
         <v>838</v>
       </c>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{642852FB-CE0F-4F8C-9C47-0DBDB6410E5F}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E81F3A82-52EC-4394-88EC-3485250A5F20}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3437" uniqueCount="1276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3449" uniqueCount="1276">
   <si>
     <t>SELECTION 1</t>
   </si>
@@ -4296,6 +4296,9 @@
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
       <c r="C2" t="s">
         <v>741</v>
       </c>
@@ -4361,6 +4364,9 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
       <c r="C3" t="s">
         <v>746</v>
       </c>
@@ -4426,6 +4432,9 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
       <c r="C4" t="s">
         <v>751</v>
       </c>
@@ -4491,6 +4500,9 @@
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
       <c r="C5" t="s">
         <v>755</v>
       </c>
@@ -4621,6 +4633,9 @@
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
       <c r="C7" t="s">
         <v>760</v>
       </c>
@@ -4751,6 +4766,9 @@
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
       <c r="C9" t="s">
         <v>764</v>
       </c>
@@ -4881,6 +4899,9 @@
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
       <c r="C11" t="s">
         <v>770</v>
       </c>
@@ -5064,6 +5085,9 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
       <c r="C14" t="s">
         <v>776</v>
       </c>
@@ -5188,6 +5212,9 @@
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
       <c r="C16" t="s">
         <v>783</v>
       </c>
@@ -5252,7 +5279,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
       <c r="C17" t="s">
         <v>787</v>
       </c>
@@ -5317,7 +5347,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C18" t="s">
         <v>789</v>
       </c>
@@ -5376,7 +5406,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
       <c r="C19" t="s">
         <v>793</v>
       </c>
@@ -5435,7 +5468,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
       <c r="C20" t="s">
         <v>797</v>
       </c>
@@ -5497,7 +5533,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C21" t="s">
         <v>800</v>
       </c>
@@ -5556,7 +5592,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C22" t="s">
         <v>803</v>
       </c>
@@ -5624,7 +5660,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C23" t="s">
         <v>807</v>
       </c>
@@ -5683,7 +5719,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C24" t="s">
         <v>809</v>
       </c>
@@ -5742,7 +5778,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C25" t="s">
         <v>812</v>
       </c>
@@ -5801,7 +5837,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C26" t="s">
         <v>815</v>
       </c>
@@ -5860,7 +5896,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C27" t="s">
         <v>819</v>
       </c>
@@ -5919,7 +5955,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C28" t="s">
         <v>822</v>
       </c>
@@ -5984,7 +6020,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C29" t="s">
         <v>826</v>
       </c>
@@ -6049,7 +6085,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C30" t="s">
         <v>830</v>
       </c>
@@ -6114,7 +6150,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C31" t="s">
         <v>834</v>
       </c>
@@ -6179,7 +6215,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C32" t="s">
         <v>838</v>
       </c>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E81F3A82-52EC-4394-88EC-3485250A5F20}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E06FE49-F81A-47F2-B435-B61FEE09823C}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3449" uniqueCount="1276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3447" uniqueCount="1277">
   <si>
     <t>SELECTION 1</t>
   </si>
@@ -3861,6 +3861,9 @@
   </si>
   <si>
     <t>106</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -4296,9 +4299,6 @@
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
       <c r="C2" t="s">
         <v>741</v>
       </c>
@@ -4432,9 +4432,6 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
       <c r="C4" t="s">
         <v>751</v>
       </c>
@@ -5213,7 +5210,7 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>1276</v>
       </c>
       <c r="C16" t="s">
         <v>783</v>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\portn\OneDrive\Documents\KECB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{9919D507-212C-42D4-8523-0FF1D819BE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E06FE49-F81A-47F2-B435-B61FEE09823C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5331A24-7CDC-44E8-A74E-038DC1543C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3447" uniqueCount="1277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3437" uniqueCount="1276">
   <si>
     <t>SELECTION 1</t>
   </si>
@@ -3861,9 +3861,6 @@
   </si>
   <si>
     <t>106</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
 </sst>
 </file>
@@ -3916,10 +3913,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4364,9 +4357,6 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
       <c r="C3" t="s">
         <v>746</v>
       </c>
@@ -4497,9 +4487,6 @@
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
       <c r="C5" t="s">
         <v>755</v>
       </c>
@@ -4630,9 +4617,6 @@
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
       <c r="C7" t="s">
         <v>760</v>
       </c>
@@ -4763,9 +4747,6 @@
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
       <c r="C9" t="s">
         <v>764</v>
       </c>
@@ -4896,9 +4877,6 @@
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
       <c r="C11" t="s">
         <v>770</v>
       </c>
@@ -5082,9 +5060,6 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
       <c r="C14" t="s">
         <v>776</v>
       </c>
@@ -5209,9 +5184,6 @@
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>1276</v>
-      </c>
       <c r="C16" t="s">
         <v>783</v>
       </c>
@@ -5276,10 +5248,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C17" t="s">
         <v>787</v>
       </c>
@@ -5344,7 +5313,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C18" t="s">
         <v>789</v>
       </c>
@@ -5403,10 +5372,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
-        <v>24</v>
-      </c>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C19" t="s">
         <v>793</v>
       </c>
@@ -5465,10 +5431,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>24</v>
-      </c>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C20" t="s">
         <v>797</v>
       </c>
@@ -5530,7 +5493,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C21" t="s">
         <v>800</v>
       </c>
@@ -5589,7 +5552,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C22" t="s">
         <v>803</v>
       </c>
@@ -5657,7 +5620,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C23" t="s">
         <v>807</v>
       </c>
@@ -5716,7 +5679,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C24" t="s">
         <v>809</v>
       </c>
@@ -5775,7 +5738,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C25" t="s">
         <v>812</v>
       </c>
@@ -5834,7 +5797,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C26" t="s">
         <v>815</v>
       </c>
@@ -5893,7 +5856,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C27" t="s">
         <v>819</v>
       </c>
@@ -5952,7 +5915,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C28" t="s">
         <v>822</v>
       </c>
@@ -6017,7 +5980,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C29" t="s">
         <v>826</v>
       </c>
@@ -6082,7 +6045,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C30" t="s">
         <v>830</v>
       </c>
@@ -6147,7 +6110,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C31" t="s">
         <v>834</v>
       </c>
@@ -6212,7 +6175,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="3:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C32" t="s">
         <v>838</v>
       </c>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\portn\OneDrive\Documents\KECB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5331A24-7CDC-44E8-A74E-038DC1543C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96209C5-4D2C-4A8D-BA8A-E504DAB37973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3437" uniqueCount="1276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3509" uniqueCount="1276">
   <si>
     <t>SELECTION 1</t>
   </si>
@@ -4357,6 +4357,9 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
       <c r="C3" t="s">
         <v>746</v>
       </c>
@@ -4422,6 +4425,9 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
       <c r="C4" t="s">
         <v>751</v>
       </c>
@@ -4617,6 +4623,9 @@
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
       <c r="C7" t="s">
         <v>760</v>
       </c>
@@ -4682,6 +4691,9 @@
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
       <c r="C8" t="s">
         <v>762</v>
       </c>
@@ -4747,6 +4759,9 @@
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
       <c r="C9" t="s">
         <v>764</v>
       </c>
@@ -4812,6 +4827,9 @@
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
       <c r="C10" t="s">
         <v>749</v>
       </c>
@@ -4942,6 +4960,9 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
       <c r="C12" t="s">
         <v>767</v>
       </c>
@@ -5060,6 +5081,9 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
       <c r="C14" t="s">
         <v>776</v>
       </c>
@@ -5184,6 +5208,9 @@
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
       <c r="C16" t="s">
         <v>783</v>
       </c>
@@ -5248,7 +5275,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
       <c r="C17" t="s">
         <v>787</v>
       </c>
@@ -5313,7 +5343,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
       <c r="C18" t="s">
         <v>789</v>
       </c>
@@ -5372,7 +5405,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C19" t="s">
         <v>793</v>
       </c>
@@ -5431,7 +5464,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
       <c r="C20" t="s">
         <v>797</v>
       </c>
@@ -5493,7 +5529,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
       <c r="C21" t="s">
         <v>800</v>
       </c>
@@ -5552,7 +5591,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C22" t="s">
         <v>803</v>
       </c>
@@ -5620,7 +5659,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
       <c r="C23" t="s">
         <v>807</v>
       </c>
@@ -5679,7 +5721,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C24" t="s">
         <v>809</v>
       </c>
@@ -5738,7 +5780,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
       <c r="C25" t="s">
         <v>812</v>
       </c>
@@ -5797,7 +5842,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
       <c r="C26" t="s">
         <v>815</v>
       </c>
@@ -5856,7 +5904,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C27" t="s">
         <v>819</v>
       </c>
@@ -5915,7 +5963,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
       <c r="C28" t="s">
         <v>822</v>
       </c>
@@ -5980,7 +6031,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C29" t="s">
         <v>826</v>
       </c>
@@ -6045,7 +6096,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C30" t="s">
         <v>830</v>
       </c>
@@ -6110,7 +6161,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C31" t="s">
         <v>834</v>
       </c>
@@ -6175,7 +6226,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C32" t="s">
         <v>838</v>
       </c>
@@ -6240,7 +6291,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="33" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>24</v>
+      </c>
       <c r="C33" t="s">
         <v>842</v>
       </c>
@@ -6305,7 +6359,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="34" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C34" t="s">
         <v>846</v>
       </c>
@@ -6370,7 +6424,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="35" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C35" t="s">
         <v>850</v>
       </c>
@@ -6429,7 +6483,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="36" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C36" t="s">
         <v>854</v>
       </c>
@@ -6494,7 +6548,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="37" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C37" t="s">
         <v>857</v>
       </c>
@@ -6559,7 +6613,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="38" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>24</v>
+      </c>
       <c r="C38" t="s">
         <v>861</v>
       </c>
@@ -6624,7 +6681,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="39" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C39" t="s">
         <v>864</v>
       </c>
@@ -6689,7 +6746,10 @@
         <v>280</v>
       </c>
     </row>
-    <row r="40" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>24</v>
+      </c>
       <c r="C40" t="s">
         <v>867</v>
       </c>
@@ -6748,7 +6808,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="41" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>24</v>
+      </c>
       <c r="C41" t="s">
         <v>871</v>
       </c>
@@ -6816,7 +6879,10 @@
         <v>280</v>
       </c>
     </row>
-    <row r="42" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>24</v>
+      </c>
       <c r="C42" t="s">
         <v>874</v>
       </c>
@@ -6884,7 +6950,10 @@
         <v>280</v>
       </c>
     </row>
-    <row r="43" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>24</v>
+      </c>
       <c r="C43" t="s">
         <v>877</v>
       </c>
@@ -6949,7 +7018,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="44" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C44" t="s">
         <v>880</v>
       </c>
@@ -7008,7 +7077,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="45" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C45" t="s">
         <v>884</v>
       </c>
@@ -7073,7 +7142,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="46" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C46" t="s">
         <v>887</v>
       </c>
@@ -7138,7 +7207,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="47" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C47" t="s">
         <v>891</v>
       </c>
@@ -7203,7 +7272,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="48" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C48" t="s">
         <v>893</v>
       </c>
@@ -7268,7 +7337,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C49" t="s">
         <v>896</v>
       </c>
@@ -7327,7 +7396,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C50" t="s">
         <v>899</v>
       </c>
@@ -7392,7 +7461,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>24</v>
+      </c>
       <c r="C51" t="s">
         <v>901</v>
       </c>
@@ -7451,7 +7523,10 @@
         <v>280</v>
       </c>
     </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>24</v>
+      </c>
       <c r="C52" t="s">
         <v>904</v>
       </c>
@@ -7519,7 +7594,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C53" t="s">
         <v>908</v>
       </c>
@@ -7584,7 +7659,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>24</v>
+      </c>
       <c r="C54" t="s">
         <v>912</v>
       </c>
@@ -7652,7 +7730,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C55" t="s">
         <v>915</v>
       </c>
@@ -7711,7 +7789,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C56" t="s">
         <v>919</v>
       </c>
@@ -7770,7 +7848,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C57" t="s">
         <v>923</v>
       </c>
@@ -7832,7 +7910,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>24</v>
+      </c>
       <c r="C58" t="s">
         <v>927</v>
       </c>
@@ -7897,7 +7978,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C59" t="s">
         <v>930</v>
       </c>
@@ -7962,7 +8043,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C60" t="s">
         <v>934</v>
       </c>
@@ -8027,7 +8108,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>24</v>
+      </c>
       <c r="C61" t="s">
         <v>938</v>
       </c>
@@ -8092,7 +8176,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C62" t="s">
         <v>942</v>
       </c>
@@ -8154,7 +8238,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C63" t="s">
         <v>945</v>
       </c>
@@ -8219,7 +8303,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C64" t="s">
         <v>949</v>
       </c>
@@ -8284,7 +8368,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="65" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>24</v>
+      </c>
       <c r="C65" t="s">
         <v>951</v>
       </c>
@@ -8349,7 +8436,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="66" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C66" t="s">
         <v>954</v>
       </c>
@@ -8408,7 +8495,10 @@
         <v>280</v>
       </c>
     </row>
-    <row r="67" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
+        <v>24</v>
+      </c>
       <c r="C67" t="s">
         <v>956</v>
       </c>
@@ -8467,7 +8557,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="68" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" t="s">
+        <v>24</v>
+      </c>
       <c r="C68" t="s">
         <v>958</v>
       </c>
@@ -8532,7 +8625,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="69" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" t="s">
+        <v>24</v>
+      </c>
       <c r="C69" t="s">
         <v>961</v>
       </c>
@@ -8591,7 +8687,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="70" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C70" t="s">
         <v>964</v>
       </c>
@@ -8653,7 +8749,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="71" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" t="s">
+        <v>24</v>
+      </c>
       <c r="C71" t="s">
         <v>967</v>
       </c>
@@ -8721,7 +8820,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="72" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C72" t="s">
         <v>971</v>
       </c>
@@ -8789,7 +8888,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="73" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" t="s">
+        <v>24</v>
+      </c>
       <c r="C73" t="s">
         <v>974</v>
       </c>
@@ -8854,7 +8956,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="74" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C74" t="s">
         <v>978</v>
       </c>
@@ -8919,7 +9021,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="75" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" t="s">
+        <v>24</v>
+      </c>
       <c r="C75" t="s">
         <v>980</v>
       </c>
@@ -8984,7 +9089,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="76" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C76" t="s">
         <v>983</v>
       </c>
@@ -9043,7 +9148,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="77" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C77" t="s">
         <v>986</v>
       </c>
@@ -9108,7 +9213,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="78" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C78" t="s">
         <v>989</v>
       </c>
@@ -9167,7 +9272,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="79" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C79" t="s">
         <v>991</v>
       </c>
@@ -9232,7 +9337,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="80" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C80" t="s">
         <v>994</v>
       </c>
@@ -9291,7 +9396,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C81" t="s">
         <v>998</v>
       </c>
@@ -9356,7 +9461,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C82" t="s">
         <v>1001</v>
       </c>
@@ -9418,7 +9523,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C83" t="s">
         <v>1005</v>
       </c>
@@ -9483,7 +9588,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C84" t="s">
         <v>1007</v>
       </c>
@@ -9542,7 +9647,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C85" t="s">
         <v>1009</v>
       </c>
@@ -9601,7 +9706,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C86" t="s">
         <v>1012</v>
       </c>
@@ -9660,7 +9765,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C87" t="s">
         <v>1014</v>
       </c>
@@ -9725,7 +9830,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C88" t="s">
         <v>1017</v>
       </c>
@@ -9790,7 +9895,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" t="s">
+        <v>24</v>
+      </c>
       <c r="C89" t="s">
         <v>1019</v>
       </c>
@@ -9855,7 +9963,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C90" t="s">
         <v>1022</v>
       </c>
@@ -9920,7 +10028,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C91" t="s">
         <v>1024</v>
       </c>
@@ -9979,7 +10087,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C92" t="s">
         <v>1027</v>
       </c>
@@ -10047,7 +10155,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" t="s">
+        <v>24</v>
+      </c>
       <c r="C93" t="s">
         <v>1030</v>
       </c>
@@ -10112,7 +10223,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" t="s">
+        <v>24</v>
+      </c>
       <c r="C94" t="s">
         <v>1033</v>
       </c>
@@ -10177,7 +10291,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" t="s">
+        <v>24</v>
+      </c>
       <c r="C95" t="s">
         <v>1036</v>
       </c>
@@ -10242,7 +10359,10 @@
         <v>280</v>
       </c>
     </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" t="s">
+        <v>24</v>
+      </c>
       <c r="C96" t="s">
         <v>1039</v>
       </c>
@@ -10307,7 +10427,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C97" t="s">
         <v>1041</v>
       </c>
@@ -10372,7 +10492,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C98" t="s">
         <v>1045</v>
       </c>
@@ -10437,7 +10557,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" t="s">
+        <v>24</v>
+      </c>
       <c r="C99" t="s">
         <v>1049</v>
       </c>
@@ -10502,7 +10625,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" t="s">
+        <v>24</v>
+      </c>
       <c r="C100" t="s">
         <v>1051</v>
       </c>
@@ -10567,7 +10693,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C101" t="s">
         <v>1054</v>
       </c>
@@ -10632,7 +10758,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C102" t="s">
         <v>1058</v>
       </c>
@@ -10697,7 +10823,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="103" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" t="s">
+        <v>24</v>
+      </c>
       <c r="C103" t="s">
         <v>1060</v>
       </c>
@@ -10762,7 +10891,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="104" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" t="s">
+        <v>24</v>
+      </c>
       <c r="C104" t="s">
         <v>1064</v>
       </c>
@@ -10827,7 +10959,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="105" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C105" t="s">
         <v>1067</v>
       </c>
@@ -10892,7 +11024,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="106" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C106" t="s">
         <v>1069</v>
       </c>
@@ -10957,7 +11089,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="107" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C107" t="s">
         <v>1275</v>
       </c>
@@ -11016,7 +11148,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="108" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" t="s">
+        <v>24</v>
+      </c>
       <c r="C108" t="s">
         <v>1073</v>
       </c>
@@ -11081,7 +11216,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="109" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C109" t="s">
         <v>1077</v>
       </c>
@@ -11146,7 +11281,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="110" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" t="s">
+        <v>24</v>
+      </c>
       <c r="C110" t="s">
         <v>1081</v>
       </c>
@@ -11211,7 +11349,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="111" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" t="s">
+        <v>24</v>
+      </c>
       <c r="C111" t="s">
         <v>1083</v>
       </c>
@@ -11276,7 +11417,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="112" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C112" t="s">
         <v>1085</v>
       </c>
@@ -11341,7 +11482,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="113" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C113" t="s">
         <v>1088</v>
       </c>
@@ -11406,7 +11547,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="114" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C114" t="s">
         <v>1090</v>
       </c>
@@ -11471,7 +11612,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="115" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C115" t="s">
         <v>1092</v>
       </c>
@@ -11530,7 +11671,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="116" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" t="s">
+        <v>24</v>
+      </c>
       <c r="C116" t="s">
         <v>1096</v>
       </c>
@@ -11598,7 +11742,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="117" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C117" t="s">
         <v>1100</v>
       </c>
@@ -11663,7 +11807,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="118" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C118" t="s">
         <v>1103</v>
       </c>
@@ -11728,7 +11872,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="119" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" t="s">
+        <v>24</v>
+      </c>
       <c r="C119" t="s">
         <v>1105</v>
       </c>
@@ -11793,7 +11940,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="120" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C120" t="s">
         <v>1109</v>
       </c>
@@ -11852,7 +11999,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="121" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C121" t="s">
         <v>1113</v>
       </c>
@@ -11911,7 +12058,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="122" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" t="s">
+        <v>24</v>
+      </c>
       <c r="C122" t="s">
         <v>1116</v>
       </c>
@@ -11976,7 +12126,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="123" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C123" t="s">
         <v>1118</v>
       </c>
@@ -12035,7 +12185,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="124" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C124" t="s">
         <v>1120</v>
       </c>
@@ -12094,7 +12244,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="125" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C125" t="s">
         <v>1121</v>
       </c>
@@ -12153,7 +12303,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="126" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C126" t="s">
         <v>1125</v>
       </c>
@@ -12212,7 +12362,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="127" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" t="s">
+        <v>24</v>
+      </c>
       <c r="C127" t="s">
         <v>1127</v>
       </c>
@@ -12274,7 +12427,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="128" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C128" t="s">
         <v>1131</v>
       </c>
@@ -12336,7 +12489,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="129" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" t="s">
+        <v>24</v>
+      </c>
       <c r="C129" t="s">
         <v>1134</v>
       </c>
@@ -12398,7 +12554,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="130" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" t="s">
+        <v>24</v>
+      </c>
       <c r="C130" t="s">
         <v>1137</v>
       </c>
@@ -12457,7 +12616,10 @@
         <v>280</v>
       </c>
     </row>
-    <row r="131" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" t="s">
+        <v>24</v>
+      </c>
       <c r="C131" t="s">
         <v>1140</v>
       </c>
@@ -12516,7 +12678,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="132" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" t="s">
+        <v>24</v>
+      </c>
       <c r="C132" t="s">
         <v>1143</v>
       </c>
@@ -12581,7 +12746,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="133" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133" t="s">
+        <v>24</v>
+      </c>
       <c r="C133" t="s">
         <v>1147</v>
       </c>
@@ -12643,7 +12811,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="134" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134" t="s">
+        <v>24</v>
+      </c>
       <c r="C134" t="s">
         <v>1150</v>
       </c>
@@ -12708,7 +12879,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="135" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C135" t="s">
         <v>1153</v>
       </c>
@@ -12770,7 +12941,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="136" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C136" t="s">
         <v>1155</v>
       </c>
@@ -12835,7 +13006,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="137" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A137" t="s">
+        <v>24</v>
+      </c>
       <c r="C137" t="s">
         <v>1158</v>
       </c>
@@ -12897,7 +13071,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="138" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A138" t="s">
+        <v>24</v>
+      </c>
       <c r="C138" t="s">
         <v>1160</v>
       </c>
@@ -12959,7 +13136,10 @@
         <v>308</v>
       </c>
     </row>
-    <row r="139" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A139" t="s">
+        <v>24</v>
+      </c>
       <c r="C139" t="s">
         <v>1162</v>
       </c>
@@ -13024,7 +13204,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="140" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C140" t="s">
         <v>1166</v>
       </c>
@@ -13089,7 +13269,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="141" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A141" t="s">
+        <v>24</v>
+      </c>
       <c r="C141" t="s">
         <v>1170</v>
       </c>
@@ -13151,7 +13334,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="142" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C142" t="s">
         <v>1174</v>
       </c>
@@ -13216,7 +13399,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="143" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C143" t="s">
         <v>1176</v>
       </c>
@@ -13281,7 +13464,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="144" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A144" t="s">
+        <v>24</v>
+      </c>
       <c r="C144" t="s">
         <v>1178</v>
       </c>
@@ -13340,7 +13526,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="145" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C145" t="s">
         <v>1181</v>
       </c>
@@ -13399,7 +13585,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="146" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A146" t="s">
+        <v>24</v>
+      </c>
       <c r="C146" t="s">
         <v>1185</v>
       </c>
@@ -13458,7 +13647,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="147" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C147" t="s">
         <v>1186</v>
       </c>
@@ -13523,7 +13712,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="148" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A148" t="s">
+        <v>24</v>
+      </c>
       <c r="C148" t="s">
         <v>1188</v>
       </c>
@@ -13582,7 +13774,10 @@
         <v>280</v>
       </c>
     </row>
-    <row r="149" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A149" t="s">
+        <v>24</v>
+      </c>
       <c r="C149" t="s">
         <v>1192</v>
       </c>
@@ -13641,7 +13836,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="150" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C150" t="s">
         <v>1195</v>
       </c>
@@ -13706,7 +13901,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="151" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C151" t="s">
         <v>1199</v>
       </c>
@@ -13771,7 +13966,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="152" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A152" t="s">
+        <v>24</v>
+      </c>
       <c r="C152" t="s">
         <v>1202</v>
       </c>
@@ -13836,7 +14034,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="153" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A153" t="s">
+        <v>24</v>
+      </c>
       <c r="C153" t="s">
         <v>1204</v>
       </c>
@@ -13901,7 +14102,10 @@
         <v>279</v>
       </c>
     </row>
-    <row r="154" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A154" t="s">
+        <v>24</v>
+      </c>
       <c r="C154" t="s">
         <v>1207</v>
       </c>
@@ -13966,7 +14170,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="155" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C155" t="s">
         <v>1210</v>
       </c>
@@ -14031,7 +14235,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="156" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A156" t="s">
+        <v>24</v>
+      </c>
       <c r="C156" t="s">
         <v>1214</v>
       </c>
@@ -14096,7 +14303,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="157" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C157" t="s">
         <v>1217</v>
       </c>
@@ -14161,7 +14368,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="158" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A158" t="s">
+        <v>24</v>
+      </c>
       <c r="C158" t="s">
         <v>1220</v>
       </c>
@@ -14226,7 +14436,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="159" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C159" t="s">
         <v>1223</v>
       </c>
@@ -14291,7 +14501,10 @@
         <v>302</v>
       </c>
     </row>
-    <row r="160" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A160" t="s">
+        <v>24</v>
+      </c>
       <c r="C160" t="s">
         <v>1226</v>
       </c>
@@ -14356,7 +14569,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="161" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C161" t="s">
         <v>1229</v>
       </c>
@@ -14421,7 +14634,10 @@
         <v>312</v>
       </c>
     </row>
-    <row r="162" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A162" t="s">
+        <v>24</v>
+      </c>
       <c r="C162" t="s">
         <v>1232</v>
       </c>
@@ -14486,7 +14702,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="163" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C163" t="s">
         <v>1236</v>
       </c>
@@ -14545,7 +14761,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="164" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C164" t="s">
         <v>1239</v>
       </c>
@@ -14610,7 +14826,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="165" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C165" t="s">
         <v>1249</v>
       </c>
@@ -14675,7 +14891,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="166" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C166" t="s">
         <v>1255</v>
       </c>
@@ -14734,7 +14950,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="167" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C167" t="s">
         <v>1260</v>
       </c>
@@ -14799,7 +15015,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="168" spans="3:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="C168" t="s">
         <v>1270</v>
       </c>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\portn\OneDrive\Documents\KECB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/So/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96209C5-4D2C-4A8D-BA8A-E504DAB37973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB43E42A-54AA-4AC6-9A3B-24B75A2AE935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/So/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/So/bis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB43E42A-54AA-4AC6-9A3B-24B75A2AE935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{20D0EE37-5B06-4F9E-BF7B-B0FC77219AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5E3821F-FEBA-449A-B346-E74E7C9840FC}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3509" uniqueCount="1276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3576" uniqueCount="1276">
   <si>
     <t>SELECTION 1</t>
   </si>
@@ -4292,6 +4292,9 @@
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
       <c r="C2" t="s">
         <v>741</v>
       </c>
@@ -4426,6 +4429,9 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
@@ -4558,6 +4564,9 @@
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
       <c r="C6" t="s">
         <v>745</v>
       </c>
@@ -4762,6 +4771,9 @@
       <c r="A9" t="s">
         <v>24</v>
       </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
       <c r="C9" t="s">
         <v>764</v>
       </c>
@@ -4828,6 +4840,9 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
@@ -5084,6 +5099,9 @@
       <c r="A14" t="s">
         <v>24</v>
       </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
       <c r="C14" t="s">
         <v>776</v>
       </c>
@@ -5211,6 +5229,9 @@
       <c r="A16" t="s">
         <v>24</v>
       </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
       <c r="C16" t="s">
         <v>783</v>
       </c>
@@ -5277,6 +5298,9 @@
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
@@ -5967,6 +5991,9 @@
       <c r="A28" t="s">
         <v>24</v>
       </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
       <c r="C28" t="s">
         <v>822</v>
       </c>
@@ -6162,6 +6189,9 @@
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
       <c r="C31" t="s">
         <v>834</v>
       </c>
@@ -6227,6 +6257,9 @@
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
       <c r="C32" t="s">
         <v>838</v>
       </c>
@@ -6425,6 +6458,9 @@
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
       <c r="C35" t="s">
         <v>850</v>
       </c>
@@ -6484,6 +6520,9 @@
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
       <c r="C36" t="s">
         <v>854</v>
       </c>
@@ -6617,6 +6656,9 @@
       <c r="A38" t="s">
         <v>24</v>
       </c>
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
       <c r="C38" t="s">
         <v>861</v>
       </c>
@@ -6812,6 +6854,9 @@
       <c r="A41" t="s">
         <v>24</v>
       </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
       <c r="C41" t="s">
         <v>871</v>
       </c>
@@ -6881,6 +6926,9 @@
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" t="s">
         <v>24</v>
       </c>
       <c r="C42" t="s">
@@ -7078,6 +7126,9 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
       <c r="C45" t="s">
         <v>884</v>
       </c>
@@ -7143,6 +7194,9 @@
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
       <c r="C46" t="s">
         <v>887</v>
       </c>
@@ -7731,6 +7785,9 @@
       </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" t="s">
+        <v>24</v>
+      </c>
       <c r="C55" t="s">
         <v>915</v>
       </c>
@@ -7914,6 +7971,9 @@
       <c r="A58" t="s">
         <v>24</v>
       </c>
+      <c r="B58" t="s">
+        <v>24</v>
+      </c>
       <c r="C58" t="s">
         <v>927</v>
       </c>
@@ -8112,6 +8172,9 @@
       <c r="A61" t="s">
         <v>24</v>
       </c>
+      <c r="B61" t="s">
+        <v>24</v>
+      </c>
       <c r="C61" t="s">
         <v>938</v>
       </c>
@@ -8177,6 +8240,9 @@
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" t="s">
+        <v>24</v>
+      </c>
       <c r="C62" t="s">
         <v>942</v>
       </c>
@@ -8239,6 +8305,9 @@
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
       <c r="C63" t="s">
         <v>945</v>
       </c>
@@ -8372,6 +8441,9 @@
       <c r="A65" t="s">
         <v>24</v>
       </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
       <c r="C65" t="s">
         <v>951</v>
       </c>
@@ -8688,6 +8760,9 @@
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" t="s">
+        <v>24</v>
+      </c>
       <c r="C70" t="s">
         <v>964</v>
       </c>
@@ -8821,6 +8896,9 @@
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
       <c r="C72" t="s">
         <v>971</v>
       </c>
@@ -8890,6 +8968,9 @@
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
+        <v>24</v>
+      </c>
+      <c r="B73" t="s">
         <v>24</v>
       </c>
       <c r="C73" t="s">
@@ -9025,6 +9106,9 @@
       <c r="A75" t="s">
         <v>24</v>
       </c>
+      <c r="B75" t="s">
+        <v>24</v>
+      </c>
       <c r="C75" t="s">
         <v>980</v>
       </c>
@@ -9149,6 +9233,9 @@
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" t="s">
+        <v>24</v>
+      </c>
       <c r="C77" t="s">
         <v>986</v>
       </c>
@@ -9273,6 +9360,9 @@
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" t="s">
+        <v>24</v>
+      </c>
       <c r="C79" t="s">
         <v>991</v>
       </c>
@@ -9524,6 +9614,9 @@
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" t="s">
+        <v>24</v>
+      </c>
       <c r="C83" t="s">
         <v>1005</v>
       </c>
@@ -9589,6 +9682,9 @@
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
       <c r="C84" t="s">
         <v>1007</v>
       </c>
@@ -9766,6 +9862,9 @@
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" t="s">
+        <v>24</v>
+      </c>
       <c r="C87" t="s">
         <v>1014</v>
       </c>
@@ -10029,6 +10128,9 @@
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" t="s">
+        <v>24</v>
+      </c>
       <c r="C91" t="s">
         <v>1024</v>
       </c>
@@ -10088,6 +10190,9 @@
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" t="s">
+        <v>24</v>
+      </c>
       <c r="C92" t="s">
         <v>1027</v>
       </c>
@@ -10159,6 +10264,9 @@
       <c r="A93" t="s">
         <v>24</v>
       </c>
+      <c r="B93" t="s">
+        <v>24</v>
+      </c>
       <c r="C93" t="s">
         <v>1030</v>
       </c>
@@ -10363,6 +10471,9 @@
       <c r="A96" t="s">
         <v>24</v>
       </c>
+      <c r="B96" t="s">
+        <v>24</v>
+      </c>
       <c r="C96" t="s">
         <v>1039</v>
       </c>
@@ -10428,6 +10539,9 @@
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" t="s">
+        <v>24</v>
+      </c>
       <c r="C97" t="s">
         <v>1041</v>
       </c>
@@ -10561,6 +10675,9 @@
       <c r="A99" t="s">
         <v>24</v>
       </c>
+      <c r="B99" t="s">
+        <v>24</v>
+      </c>
       <c r="C99" t="s">
         <v>1049</v>
       </c>
@@ -10627,6 +10744,9 @@
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
+        <v>24</v>
+      </c>
+      <c r="B100" t="s">
         <v>24</v>
       </c>
       <c r="C100" t="s">
@@ -11090,6 +11210,9 @@
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" t="s">
+        <v>24</v>
+      </c>
       <c r="C107" t="s">
         <v>1275</v>
       </c>
@@ -11150,6 +11273,9 @@
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
+        <v>24</v>
+      </c>
+      <c r="B108" t="s">
         <v>24</v>
       </c>
       <c r="C108" t="s">
@@ -11285,6 +11411,9 @@
       <c r="A110" t="s">
         <v>24</v>
       </c>
+      <c r="B110" t="s">
+        <v>24</v>
+      </c>
       <c r="C110" t="s">
         <v>1081</v>
       </c>
@@ -11351,6 +11480,9 @@
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
+        <v>24</v>
+      </c>
+      <c r="B111" t="s">
         <v>24</v>
       </c>
       <c r="C111" t="s">
@@ -11613,6 +11745,9 @@
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" t="s">
+        <v>24</v>
+      </c>
       <c r="C115" t="s">
         <v>1092</v>
       </c>
@@ -11673,6 +11808,9 @@
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
+        <v>24</v>
+      </c>
+      <c r="B116" t="s">
         <v>24</v>
       </c>
       <c r="C116" t="s">
@@ -11941,6 +12079,9 @@
       </c>
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B120" t="s">
+        <v>24</v>
+      </c>
       <c r="C120" t="s">
         <v>1109</v>
       </c>
@@ -12000,6 +12141,9 @@
       </c>
     </row>
     <row r="121" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B121" t="s">
+        <v>24</v>
+      </c>
       <c r="C121" t="s">
         <v>1113</v>
       </c>
@@ -12304,6 +12448,9 @@
       </c>
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B126" t="s">
+        <v>24</v>
+      </c>
       <c r="C126" t="s">
         <v>1125</v>
       </c>
@@ -12364,6 +12511,9 @@
     </row>
     <row r="127" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
+        <v>24</v>
+      </c>
+      <c r="B127" t="s">
         <v>24</v>
       </c>
       <c r="C127" t="s">
@@ -12493,6 +12643,9 @@
       <c r="A129" t="s">
         <v>24</v>
       </c>
+      <c r="B129" t="s">
+        <v>24</v>
+      </c>
       <c r="C129" t="s">
         <v>1134</v>
       </c>
@@ -12682,6 +12835,9 @@
       <c r="A132" t="s">
         <v>24</v>
       </c>
+      <c r="B132" t="s">
+        <v>24</v>
+      </c>
       <c r="C132" t="s">
         <v>1143</v>
       </c>
@@ -12750,6 +12906,9 @@
       <c r="A133" t="s">
         <v>24</v>
       </c>
+      <c r="B133" t="s">
+        <v>24</v>
+      </c>
       <c r="C133" t="s">
         <v>1147</v>
       </c>
@@ -12813,6 +12972,9 @@
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
+        <v>24</v>
+      </c>
+      <c r="B134" t="s">
         <v>24</v>
       </c>
       <c r="C134" t="s">
@@ -13010,6 +13172,9 @@
       <c r="A137" t="s">
         <v>24</v>
       </c>
+      <c r="B137" t="s">
+        <v>24</v>
+      </c>
       <c r="C137" t="s">
         <v>1158</v>
       </c>
@@ -13075,6 +13240,9 @@
       <c r="A138" t="s">
         <v>24</v>
       </c>
+      <c r="B138" t="s">
+        <v>24</v>
+      </c>
       <c r="C138" t="s">
         <v>1160</v>
       </c>
@@ -13140,6 +13308,9 @@
       <c r="A139" t="s">
         <v>24</v>
       </c>
+      <c r="B139" t="s">
+        <v>24</v>
+      </c>
       <c r="C139" t="s">
         <v>1162</v>
       </c>
@@ -13205,6 +13376,9 @@
       </c>
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B140" t="s">
+        <v>24</v>
+      </c>
       <c r="C140" t="s">
         <v>1166</v>
       </c>
@@ -13902,6 +14076,9 @@
       </c>
     </row>
     <row r="151" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B151" t="s">
+        <v>24</v>
+      </c>
       <c r="C151" t="s">
         <v>1199</v>
       </c>
@@ -13970,6 +14147,9 @@
       <c r="A152" t="s">
         <v>24</v>
       </c>
+      <c r="B152" t="s">
+        <v>24</v>
+      </c>
       <c r="C152" t="s">
         <v>1202</v>
       </c>
@@ -14104,6 +14284,9 @@
     </row>
     <row r="154" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
+        <v>24</v>
+      </c>
+      <c r="B154" t="s">
         <v>24</v>
       </c>
       <c r="C154" t="s">
@@ -14239,6 +14422,9 @@
       <c r="A156" t="s">
         <v>24</v>
       </c>
+      <c r="B156" t="s">
+        <v>24</v>
+      </c>
       <c r="C156" t="s">
         <v>1214</v>
       </c>
@@ -14372,6 +14558,9 @@
       <c r="A158" t="s">
         <v>24</v>
       </c>
+      <c r="B158" t="s">
+        <v>24</v>
+      </c>
       <c r="C158" t="s">
         <v>1220</v>
       </c>
@@ -14505,6 +14694,9 @@
       <c r="A160" t="s">
         <v>24</v>
       </c>
+      <c r="B160" t="s">
+        <v>24</v>
+      </c>
       <c r="C160" t="s">
         <v>1226</v>
       </c>
@@ -14638,6 +14830,9 @@
       <c r="A162" t="s">
         <v>24</v>
       </c>
+      <c r="B162" t="s">
+        <v>24</v>
+      </c>
       <c r="C162" t="s">
         <v>1232</v>
       </c>
@@ -14762,6 +14957,9 @@
       </c>
     </row>
     <row r="164" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B164" t="s">
+        <v>24</v>
+      </c>
       <c r="C164" t="s">
         <v>1239</v>
       </c>
@@ -14827,6 +15025,9 @@
       </c>
     </row>
     <row r="165" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B165" t="s">
+        <v>24</v>
+      </c>
       <c r="C165" t="s">
         <v>1249</v>
       </c>

--- a/2026.xlsx
+++ b/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96446654622f8372/Ausstellung Burgdorf 2026/Drucken/App/So/bis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{20D0EE37-5B06-4F9E-BF7B-B0FC77219AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5E3821F-FEBA-449A-B346-E74E7C9840FC}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{20D0EE37-5B06-4F9E-BF7B-B0FC77219AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD999068-5904-4E92-AE5E-441DD89C727D}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3913,6 +3913,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4703,6 +4707,9 @@
       <c r="A8" t="s">
         <v>24</v>
       </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
       <c r="C8" t="s">
         <v>762</v>
       </c>
@@ -4840,9 +4847,6 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
